--- a/grupos/6APM - Estadisticos 20212.xlsx
+++ b/grupos/6APM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="119">
   <si>
     <t>Materia</t>
   </si>
@@ -952,7 +952,7 @@
         <v>7</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H5">
         <v>-1</v>
@@ -1006,7 +1006,7 @@
         <v>7</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1183,7 +1183,7 @@
         <v>5</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H8">
         <v>-1</v>
@@ -1237,7 +1237,7 @@
         <v>5</v>
       </c>
       <c r="Y8">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1491,7 +1491,7 @@
         <v>5</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H12">
         <v>-1</v>
@@ -1545,7 +1545,7 @@
         <v>5</v>
       </c>
       <c r="Y12">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1722,7 +1722,7 @@
         <v>10</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H15">
         <v>-1</v>
@@ -1776,7 +1776,7 @@
         <v>10</v>
       </c>
       <c r="Y15">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1799,7 +1799,7 @@
         <v>5</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H16">
         <v>-1</v>
@@ -1853,7 +1853,7 @@
         <v>5</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1876,7 +1876,7 @@
         <v>6</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H17">
         <v>-1</v>
@@ -1930,7 +1930,7 @@
         <v>6</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2794,22 +2794,25 @@
         <v>24</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
+      <c r="H3">
+        <v>6.7</v>
+      </c>
       <c r="I3">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J3">
-        <v>100</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -2947,7 +2950,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3036,22 +3039,22 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>19330051920430</v>
+        <v>19330051920225</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3068,30 +3071,30 @@
         <v>97</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>19330051920225</v>
+        <v>19330051920226</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3108,44 +3111,44 @@
         <v>98</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>19330051920226</v>
+        <v>19330051920227</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>19330051920227</v>
+        <v>19330051920229</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C10" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="D10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -3156,16 +3159,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>19330051920227</v>
+        <v>19330051920229</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C11" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="D11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -3176,16 +3179,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>19330051920229</v>
+        <v>19330051920230</v>
       </c>
       <c r="B12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C12" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="D12" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -3196,16 +3199,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>19330051920229</v>
+        <v>19330051920230</v>
       </c>
       <c r="B13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C13" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="D13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -3216,16 +3219,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>19330051920230</v>
+        <v>19330051920231</v>
       </c>
       <c r="B14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C14" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="D14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -3236,36 +3239,36 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>19330051920230</v>
+        <v>19330051920231</v>
       </c>
       <c r="B15" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C15" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="D15" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F15" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>19330051920231</v>
+        <v>19330051920232</v>
       </c>
       <c r="B16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C16" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="D16" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -3276,76 +3279,76 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>19330051920231</v>
+        <v>19330051920232</v>
       </c>
       <c r="B17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C17" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="D17" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E17" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>19330051920231</v>
+        <v>19330051920233</v>
       </c>
       <c r="B18" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C18" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="D18" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E18" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>19330051920232</v>
+        <v>19330051920233</v>
       </c>
       <c r="B19" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F19" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>19330051920232</v>
+        <v>19330051920233</v>
       </c>
       <c r="B20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C20" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E20" t="s">
         <v>10</v>
@@ -3356,16 +3359,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>19330051920233</v>
+        <v>19330051920234</v>
       </c>
       <c r="B21" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C21" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D21" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -3376,176 +3379,176 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>19330051920233</v>
+        <v>19330051920429</v>
       </c>
       <c r="B22" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C22" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D22" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E22" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>19330051920233</v>
+        <v>19330051920235</v>
       </c>
       <c r="B23" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C23" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D23" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E23" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>19330051920234</v>
+        <v>19330051920235</v>
       </c>
       <c r="B24" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C24" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D24" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E24" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F24" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>19330051920234</v>
+        <v>19330051920236</v>
       </c>
       <c r="B25" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C25" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="D25" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E25" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>19330051920429</v>
+        <v>19330051920236</v>
       </c>
       <c r="B26" t="s">
+        <v>68</v>
+      </c>
+      <c r="C26" t="s">
         <v>66</v>
       </c>
-      <c r="C26" t="s">
-        <v>88</v>
-      </c>
       <c r="D26" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E26" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F26" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>19330051920429</v>
+        <v>19330051920237</v>
       </c>
       <c r="B27" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C27" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="D27" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E27" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>19330051920235</v>
+        <v>19330051920237</v>
       </c>
       <c r="B28" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C28" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E28" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F28" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>19330051920235</v>
+        <v>19330051920228</v>
       </c>
       <c r="B29" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C29" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="D29" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E29" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F29" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>19330051920235</v>
+        <v>19330051920228</v>
       </c>
       <c r="B30" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C30" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="D30" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E30" t="s">
         <v>10</v>
@@ -3556,16 +3559,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>19330051920236</v>
+        <v>19330051420227</v>
       </c>
       <c r="B31" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C31" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D31" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
@@ -3576,16 +3579,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>19330051920236</v>
+        <v>19330051420227</v>
       </c>
       <c r="B32" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C32" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D32" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E32" t="s">
         <v>10</v>
@@ -3596,16 +3599,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>19330051920237</v>
+        <v>19330051920404</v>
       </c>
       <c r="B33" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C33" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="D33" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
@@ -3616,16 +3619,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>19330051920237</v>
+        <v>19330051920404</v>
       </c>
       <c r="B34" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C34" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="D34" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E34" t="s">
         <v>10</v>
@@ -3636,16 +3639,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>19330051920228</v>
+        <v>19330051920240</v>
       </c>
       <c r="B35" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C35" t="s">
-        <v>89</v>
+        <v>64</v>
       </c>
       <c r="D35" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -3656,16 +3659,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>19330051920228</v>
+        <v>19330051920240</v>
       </c>
       <c r="B36" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C36" t="s">
-        <v>89</v>
+        <v>64</v>
       </c>
       <c r="D36" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E36" t="s">
         <v>10</v>
@@ -3676,16 +3679,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <v>19330051420227</v>
+        <v>19330051920239</v>
       </c>
       <c r="B37" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C37" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D37" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
@@ -3696,16 +3699,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38">
-        <v>19330051420227</v>
+        <v>19330051920239</v>
       </c>
       <c r="B38" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C38" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D38" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E38" t="s">
         <v>10</v>
@@ -3716,16 +3719,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39">
-        <v>19330051920404</v>
+        <v>19330051920242</v>
       </c>
       <c r="B39" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C39" t="s">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="D39" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
@@ -3736,16 +3739,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40">
-        <v>19330051920404</v>
+        <v>19330051920242</v>
       </c>
       <c r="B40" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C40" t="s">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="D40" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E40" t="s">
         <v>10</v>
@@ -3756,16 +3759,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41">
-        <v>19330051920240</v>
+        <v>19330051920243</v>
       </c>
       <c r="B41" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C41" t="s">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="D41" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
@@ -3776,241 +3779,121 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42">
-        <v>19330051920240</v>
+        <v>19330051920243</v>
       </c>
       <c r="B42" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C42" t="s">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="D42" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E42" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F42" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43">
-        <v>19330051920239</v>
+        <v>19330051920243</v>
       </c>
       <c r="B43" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C43" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D43" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E43" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F43" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44">
-        <v>19330051920239</v>
+        <v>19330051920244</v>
       </c>
       <c r="B44" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C44" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="D44" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E44" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F44" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45">
-        <v>19330051920242</v>
+        <v>19330051920244</v>
       </c>
       <c r="B45" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C45" t="s">
         <v>66</v>
       </c>
       <c r="D45" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E45" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F45" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46">
-        <v>19330051920242</v>
+        <v>19330051920245</v>
       </c>
       <c r="B46" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C46" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="D46" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E46" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F46" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47">
-        <v>19330051920243</v>
+        <v>19330051920245</v>
       </c>
       <c r="B47" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C47" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D47" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E47" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F47" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>19330051920243</v>
-      </c>
-      <c r="B48" t="s">
-        <v>76</v>
-      </c>
-      <c r="C48" t="s">
-        <v>93</v>
-      </c>
-      <c r="D48" t="s">
-        <v>116</v>
-      </c>
-      <c r="E48" t="s">
-        <v>7</v>
-      </c>
-      <c r="F48" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>19330051920243</v>
-      </c>
-      <c r="B49" t="s">
-        <v>76</v>
-      </c>
-      <c r="C49" t="s">
-        <v>93</v>
-      </c>
-      <c r="D49" t="s">
-        <v>116</v>
-      </c>
-      <c r="E49" t="s">
-        <v>10</v>
-      </c>
-      <c r="F49" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>19330051920244</v>
-      </c>
-      <c r="B50" t="s">
-        <v>77</v>
-      </c>
-      <c r="C50" t="s">
-        <v>66</v>
-      </c>
-      <c r="D50" t="s">
-        <v>117</v>
-      </c>
-      <c r="E50" t="s">
-        <v>8</v>
-      </c>
-      <c r="F50" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>19330051920244</v>
-      </c>
-      <c r="B51" t="s">
-        <v>77</v>
-      </c>
-      <c r="C51" t="s">
-        <v>66</v>
-      </c>
-      <c r="D51" t="s">
-        <v>117</v>
-      </c>
-      <c r="E51" t="s">
-        <v>10</v>
-      </c>
-      <c r="F51" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>19330051920245</v>
-      </c>
-      <c r="B52" t="s">
-        <v>78</v>
-      </c>
-      <c r="C52" t="s">
-        <v>94</v>
-      </c>
-      <c r="D52" t="s">
-        <v>118</v>
-      </c>
-      <c r="E52" t="s">
-        <v>8</v>
-      </c>
-      <c r="F52" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>19330051920245</v>
-      </c>
-      <c r="B53" t="s">
-        <v>78</v>
-      </c>
-      <c r="C53" t="s">
-        <v>94</v>
-      </c>
-      <c r="D53" t="s">
-        <v>118</v>
-      </c>
-      <c r="E53" t="s">
-        <v>10</v>
-      </c>
-      <c r="F53" t="s">
         <v>46</v>
       </c>
     </row>
@@ -4047,16 +3930,16 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>19330051920231</v>
+        <v>19330051920233</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="D2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -4064,16 +3947,16 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920233</v>
+        <v>19330051920243</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="D3" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -4081,50 +3964,50 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920235</v>
+        <v>19330051920223</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920243</v>
+        <v>19330051920225</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920223</v>
+        <v>19330051920226</v>
       </c>
       <c r="B6" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D6" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -4132,16 +4015,16 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920430</v>
+        <v>19330051920229</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E7">
         <v>2</v>
@@ -4149,16 +4032,16 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920225</v>
+        <v>19330051920230</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C8" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E8">
         <v>2</v>
@@ -4166,16 +4049,16 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920226</v>
+        <v>19330051920231</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="D9" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E9">
         <v>2</v>
@@ -4183,16 +4066,16 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920227</v>
+        <v>19330051920232</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D10" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -4200,16 +4083,16 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920229</v>
+        <v>19330051920235</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="C11" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="D11" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -4217,16 +4100,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920230</v>
+        <v>19330051920236</v>
       </c>
       <c r="B12" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="D12" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -4234,16 +4117,16 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920232</v>
+        <v>19330051920237</v>
       </c>
       <c r="B13" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C13" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="D13" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -4251,16 +4134,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920234</v>
+        <v>19330051920228</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C14" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D14" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E14">
         <v>2</v>
@@ -4268,16 +4151,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920429</v>
+        <v>19330051420227</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D15" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E15">
         <v>2</v>
@@ -4285,16 +4168,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920236</v>
+        <v>19330051920404</v>
       </c>
       <c r="B16" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C16" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="D16" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E16">
         <v>2</v>
@@ -4302,16 +4185,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920237</v>
+        <v>19330051920240</v>
       </c>
       <c r="B17" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C17" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D17" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E17">
         <v>2</v>
@@ -4319,16 +4202,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920228</v>
+        <v>19330051920239</v>
       </c>
       <c r="B18" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C18" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D18" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E18">
         <v>2</v>
@@ -4336,16 +4219,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051420227</v>
+        <v>19330051920242</v>
       </c>
       <c r="B19" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C19" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="D19" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E19">
         <v>2</v>
@@ -4353,16 +4236,16 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920404</v>
+        <v>19330051920244</v>
       </c>
       <c r="B20" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C20" t="s">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="D20" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="E20">
         <v>2</v>
@@ -4370,16 +4253,16 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920240</v>
+        <v>19330051920245</v>
       </c>
       <c r="B21" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C21" t="s">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="D21" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E21">
         <v>2</v>
@@ -4387,70 +4270,70 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920239</v>
+        <v>19330051920430</v>
       </c>
       <c r="B22" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="C22" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D22" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920242</v>
+        <v>19330051920227</v>
       </c>
       <c r="B23" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="C23" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="D23" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>19330051920244</v>
+        <v>19330051920234</v>
       </c>
       <c r="B24" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="C24" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="D24" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>19330051920245</v>
+        <v>19330051920429</v>
       </c>
       <c r="B25" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C25" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D25" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4460,7 +4343,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4538,16 +4421,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920430</v>
+        <v>19330051920225</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -4561,16 +4444,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920430</v>
+        <v>19330051920225</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -4584,16 +4467,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920225</v>
+        <v>19330051920229</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C6" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="D6" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -4607,16 +4490,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920225</v>
+        <v>19330051920229</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -4630,16 +4513,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920229</v>
+        <v>19330051920230</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C8" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -4653,16 +4536,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920229</v>
+        <v>19330051920230</v>
       </c>
       <c r="B9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="D9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -4676,16 +4559,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920230</v>
+        <v>19330051920232</v>
       </c>
       <c r="B10" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D10" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -4699,16 +4582,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920230</v>
+        <v>19330051920232</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D11" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -4722,16 +4605,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920232</v>
+        <v>19330051920236</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C12" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="D12" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -4745,16 +4628,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920232</v>
+        <v>19330051920236</v>
       </c>
       <c r="B13" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C13" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="D13" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -4768,16 +4651,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19330051920234</v>
+        <v>19330051920228</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C14" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D14" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -4791,16 +4674,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>19330051920234</v>
+        <v>19330051920228</v>
       </c>
       <c r="B15" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D15" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
@@ -4814,16 +4697,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>19330051920429</v>
+        <v>19330051420227</v>
       </c>
       <c r="B16" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D16" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -4837,16 +4720,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>19330051920429</v>
+        <v>19330051420227</v>
       </c>
       <c r="B17" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D17" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
@@ -4860,16 +4743,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>19330051920236</v>
+        <v>19330051920404</v>
       </c>
       <c r="B18" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C18" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="D18" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -4883,16 +4766,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>19330051920236</v>
+        <v>19330051920404</v>
       </c>
       <c r="B19" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C19" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="D19" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
@@ -4906,16 +4789,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>19330051920228</v>
+        <v>19330051920239</v>
       </c>
       <c r="B20" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C20" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D20" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -4929,16 +4812,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>19330051920228</v>
+        <v>19330051920239</v>
       </c>
       <c r="B21" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C21" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D21" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E21" t="s">
         <v>10</v>
@@ -4952,16 +4835,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>19330051420227</v>
+        <v>19330051920242</v>
       </c>
       <c r="B22" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C22" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="D22" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -4975,16 +4858,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>19330051420227</v>
+        <v>19330051920242</v>
       </c>
       <c r="B23" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C23" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="D23" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E23" t="s">
         <v>10</v>
@@ -4998,16 +4881,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>19330051920404</v>
+        <v>19330051920245</v>
       </c>
       <c r="B24" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C24" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D24" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -5021,16 +4904,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>19330051920404</v>
+        <v>19330051920245</v>
       </c>
       <c r="B25" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C25" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D25" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="E25" t="s">
         <v>10</v>
@@ -5044,16 +4927,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>19330051920239</v>
+        <v>19330051920430</v>
       </c>
       <c r="B26" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="C26" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D26" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -5067,22 +4950,22 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>19330051920239</v>
+        <v>19330051920234</v>
       </c>
       <c r="B27" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="C27" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D27" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="E27" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G27">
         <v>-1</v>
@@ -5090,16 +4973,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>19330051920242</v>
+        <v>19330051920429</v>
       </c>
       <c r="B28" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="C28" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="D28" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -5108,75 +4991,6 @@
         <v>45</v>
       </c>
       <c r="G28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>19330051920242</v>
-      </c>
-      <c r="B29" t="s">
-        <v>75</v>
-      </c>
-      <c r="C29" t="s">
-        <v>66</v>
-      </c>
-      <c r="D29" t="s">
-        <v>115</v>
-      </c>
-      <c r="E29" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" t="s">
-        <v>46</v>
-      </c>
-      <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>19330051920245</v>
-      </c>
-      <c r="B30" t="s">
-        <v>78</v>
-      </c>
-      <c r="C30" t="s">
-        <v>94</v>
-      </c>
-      <c r="D30" t="s">
-        <v>118</v>
-      </c>
-      <c r="E30" t="s">
-        <v>8</v>
-      </c>
-      <c r="F30" t="s">
-        <v>45</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>19330051920245</v>
-      </c>
-      <c r="B31" t="s">
-        <v>78</v>
-      </c>
-      <c r="C31" t="s">
-        <v>94</v>
-      </c>
-      <c r="D31" t="s">
-        <v>118</v>
-      </c>
-      <c r="E31" t="s">
-        <v>10</v>
-      </c>
-      <c r="F31" t="s">
-        <v>46</v>
-      </c>
-      <c r="G31">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/6APM - Estadisticos 20212.xlsx
+++ b/grupos/6APM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="119">
   <si>
     <t>Materia</t>
   </si>
@@ -155,24 +155,24 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Herrera Serrano Mayra Iliana</t>
+  </si>
+  <si>
     <t>Velasco Sánchez David</t>
   </si>
   <si>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
+    <t>Ortega Valle Manuel</t>
+  </si>
+  <si>
+    <t>Rodriguez Roman Marisol</t>
+  </si>
+  <si>
     <t>Duran Amezcua María Angélica</t>
   </si>
   <si>
-    <t>Herrera Serrano Mayra Iliana</t>
-  </si>
-  <si>
-    <t>Ochoa Martínez Mayeli</t>
-  </si>
-  <si>
-    <t>Ortega Valle Manuel</t>
-  </si>
-  <si>
-    <t>Rodriguez Roman Marisol</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -185,6 +185,99 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CHIPAHUA</t>
+  </si>
+  <si>
+    <t>GARIBAY</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>HERAS</t>
+  </si>
+  <si>
+    <t>LICEA</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>REYNOSO</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>PANZO</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>CALPULALPAN</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>ALCARAZ</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>LLAVE</t>
+  </si>
+  <si>
+    <t>KARLA FABIOLA</t>
+  </si>
+  <si>
+    <t>MARCOS URIEL</t>
+  </si>
+  <si>
+    <t>URIEL</t>
+  </si>
+  <si>
+    <t>YARELY JACQUELINE</t>
+  </si>
+  <si>
+    <t>CESAR ENRIQUE</t>
+  </si>
+  <si>
+    <t>QADMIEL TAMARA</t>
+  </si>
+  <si>
+    <t>ALEXANDER</t>
+  </si>
+  <si>
+    <t>RENZO JHOVANI</t>
+  </si>
+  <si>
+    <t>ABDIEL ANTONIO</t>
+  </si>
+  <si>
+    <t>DANIELA JAQUELINE</t>
+  </si>
+  <si>
+    <t>YESUA ISIDRO</t>
+  </si>
+  <si>
     <t>ALEJO</t>
   </si>
   <si>
@@ -194,9 +287,6 @@
     <t>CESPEDES</t>
   </si>
   <si>
-    <t>CHIPAHUA</t>
-  </si>
-  <si>
     <t>CHORA</t>
   </si>
   <si>
@@ -206,57 +296,24 @@
     <t>ESTRADA</t>
   </si>
   <si>
-    <t>GARIBAY</t>
-  </si>
-  <si>
     <t>GASPAR</t>
   </si>
   <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
     <t>GUTIERREZ</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>HERAS</t>
-  </si>
-  <si>
     <t>LADINO</t>
   </si>
   <si>
-    <t>LICEA</t>
-  </si>
-  <si>
     <t>DE LA LUZ</t>
   </si>
   <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>REYNOSO</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
     <t>RICO</t>
   </si>
   <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
     <t>VASQUEZ</t>
   </si>
   <si>
@@ -266,45 +323,21 @@
     <t>CRUZ</t>
   </si>
   <si>
-    <t>PANZO</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>CASTAÑEDA</t>
   </si>
   <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
-    <t>MORALES</t>
-  </si>
-  <si>
     <t>CELICEO</t>
   </si>
   <si>
-    <t>CALPULALPAN</t>
-  </si>
-  <si>
     <t>HUESCA</t>
   </si>
   <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>ALCARAZ</t>
-  </si>
-  <si>
     <t>ORTIZ</t>
   </si>
   <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>LLAVE</t>
-  </si>
-  <si>
     <t>RAUL ALEJANDRO</t>
   </si>
   <si>
@@ -314,9 +347,6 @@
     <t>ERICK MANUEL</t>
   </si>
   <si>
-    <t>KARLA FABIOLA</t>
-  </si>
-  <si>
     <t>GABRIEL ALEJANDRO</t>
   </si>
   <si>
@@ -326,39 +356,18 @@
     <t>BRAULIO VADIR</t>
   </si>
   <si>
-    <t>MARCOS URIEL</t>
-  </si>
-  <si>
     <t>VIANEY</t>
   </si>
   <si>
-    <t>URIEL</t>
-  </si>
-  <si>
     <t>PAOLA</t>
   </si>
   <si>
-    <t>YARELY JACQUELINE</t>
-  </si>
-  <si>
-    <t>CESAR ENRIQUE</t>
-  </si>
-  <si>
     <t>ZURISADAI</t>
   </si>
   <si>
-    <t>QADMIEL TAMARA</t>
-  </si>
-  <si>
     <t>FATIMA</t>
   </si>
   <si>
-    <t>ALEXANDER</t>
-  </si>
-  <si>
-    <t>RENZO JHOVANI</t>
-  </si>
-  <si>
     <t>MARIA DE JESUS</t>
   </si>
   <si>
@@ -366,15 +375,6 @@
   </si>
   <si>
     <t>ANGEL EDUARDO</t>
-  </si>
-  <si>
-    <t>ABDIEL ANTONIO</t>
-  </si>
-  <si>
-    <t>DANIELA JAQUELINE</t>
-  </si>
-  <si>
-    <t>YESUA ISIDRO</t>
   </si>
 </sst>
 </file>
@@ -869,13 +869,13 @@
         <v>8</v>
       </c>
       <c r="E4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F4">
         <v>6</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H4">
         <v>-1</v>
@@ -923,13 +923,13 @@
         <v>8</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X4">
         <v>6</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -946,7 +946,7 @@
         <v>7</v>
       </c>
       <c r="E5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F5">
         <v>7</v>
@@ -1000,7 +1000,7 @@
         <v>7</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X5">
         <v>7</v>
@@ -1023,13 +1023,13 @@
         <v>7</v>
       </c>
       <c r="E6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F6">
         <v>9</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H6">
         <v>-1</v>
@@ -1077,13 +1077,13 @@
         <v>7</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X6">
         <v>9</v>
       </c>
       <c r="Y6">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1100,7 +1100,7 @@
         <v>6</v>
       </c>
       <c r="E7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F7">
         <v>7</v>
@@ -1154,7 +1154,7 @@
         <v>6</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X7">
         <v>7</v>
@@ -1177,7 +1177,7 @@
         <v>8</v>
       </c>
       <c r="E8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -1231,7 +1231,7 @@
         <v>8</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X8">
         <v>5</v>
@@ -1254,13 +1254,13 @@
         <v>9</v>
       </c>
       <c r="E9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F9">
         <v>6</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H9">
         <v>-1</v>
@@ -1308,13 +1308,13 @@
         <v>9</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X9">
         <v>6</v>
       </c>
       <c r="Y9">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1331,13 +1331,13 @@
         <v>8</v>
       </c>
       <c r="E10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F10">
         <v>8</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H10">
         <v>-1</v>
@@ -1385,13 +1385,13 @@
         <v>8</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X10">
         <v>8</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1408,13 +1408,13 @@
         <v>8</v>
       </c>
       <c r="E11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F11">
         <v>8</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H11">
         <v>-1</v>
@@ -1462,13 +1462,13 @@
         <v>8</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X11">
         <v>8</v>
       </c>
       <c r="Y11">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1562,13 +1562,13 @@
         <v>9</v>
       </c>
       <c r="E13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F13">
         <v>9</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H13">
         <v>-1</v>
@@ -1616,13 +1616,13 @@
         <v>9</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X13">
         <v>9</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1645,7 +1645,7 @@
         <v>6</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H14">
         <v>-1</v>
@@ -1699,7 +1699,7 @@
         <v>6</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1716,7 +1716,7 @@
         <v>6</v>
       </c>
       <c r="E15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F15">
         <v>10</v>
@@ -1770,7 +1770,7 @@
         <v>6</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X15">
         <v>10</v>
@@ -1793,7 +1793,7 @@
         <v>-1</v>
       </c>
       <c r="E16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -1847,7 +1847,7 @@
         <v>-1</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X16">
         <v>5</v>
@@ -1947,13 +1947,13 @@
         <v>8</v>
       </c>
       <c r="E18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F18">
         <v>9</v>
       </c>
       <c r="G18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H18">
         <v>-1</v>
@@ -2001,13 +2001,13 @@
         <v>8</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X18">
         <v>9</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2030,7 +2030,7 @@
         <v>5</v>
       </c>
       <c r="G19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H19">
         <v>-1</v>
@@ -2084,7 +2084,7 @@
         <v>5</v>
       </c>
       <c r="Y19">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2101,7 +2101,7 @@
         <v>6</v>
       </c>
       <c r="E20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F20">
         <v>8</v>
@@ -2155,7 +2155,7 @@
         <v>6</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X20">
         <v>8</v>
@@ -2178,7 +2178,7 @@
         <v>8</v>
       </c>
       <c r="E21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F21">
         <v>7</v>
@@ -2232,7 +2232,7 @@
         <v>8</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X21">
         <v>7</v>
@@ -2255,13 +2255,13 @@
         <v>8</v>
       </c>
       <c r="E22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F22">
         <v>9</v>
       </c>
       <c r="G22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H22">
         <v>-1</v>
@@ -2309,13 +2309,13 @@
         <v>8</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X22">
         <v>9</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2332,13 +2332,13 @@
         <v>8</v>
       </c>
       <c r="E23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F23">
         <v>8</v>
       </c>
       <c r="G23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H23">
         <v>-1</v>
@@ -2386,13 +2386,13 @@
         <v>8</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X23">
         <v>8</v>
       </c>
       <c r="Y23">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2409,13 +2409,13 @@
         <v>8</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F24">
         <v>7</v>
       </c>
       <c r="G24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H24">
         <v>-1</v>
@@ -2463,13 +2463,13 @@
         <v>8</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X24">
         <v>7</v>
       </c>
       <c r="Y24">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2492,7 +2492,7 @@
         <v>5</v>
       </c>
       <c r="G25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H25">
         <v>-1</v>
@@ -2546,7 +2546,7 @@
         <v>5</v>
       </c>
       <c r="Y25">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2569,7 +2569,7 @@
         <v>5</v>
       </c>
       <c r="G26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H26">
         <v>-1</v>
@@ -2623,7 +2623,7 @@
         <v>5</v>
       </c>
       <c r="Y26">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2646,7 +2646,7 @@
         <v>9</v>
       </c>
       <c r="G27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H27">
         <v>-1</v>
@@ -2700,7 +2700,7 @@
         <v>9</v>
       </c>
       <c r="Y27">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2756,7 +2756,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>45</v>
@@ -2765,27 +2765,30 @@
         <v>24</v>
       </c>
       <c r="D2">
+        <v>16</v>
+      </c>
+      <c r="E2">
+        <v>8</v>
+      </c>
+      <c r="F2">
+        <v>66.67</v>
+      </c>
+      <c r="G2">
+        <v>33.33</v>
+      </c>
+      <c r="H2">
+        <v>6</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="E2">
+      <c r="J2">
         <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>24</v>
-      </c>
-      <c r="J2">
-        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>46</v>
@@ -2794,30 +2797,30 @@
         <v>24</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>25</v>
+        <v>70.83</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>6.7</v>
+        <v>8.1</v>
       </c>
       <c r="I3">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="J3">
-        <v>75</v>
+        <v>29.17</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>47</v>
@@ -2826,19 +2829,19 @@
         <v>24</v>
       </c>
       <c r="D4">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="G4">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="H4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -2849,7 +2852,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>48</v>
@@ -2858,30 +2861,30 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>75</v>
+        <v>83.33</v>
       </c>
       <c r="G5">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>49</v>
@@ -2893,27 +2896,27 @@
         <v>20</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F6">
         <v>83.33</v>
       </c>
       <c r="G6">
+        <v>16.67</v>
+      </c>
+      <c r="H6">
+        <v>7.4</v>
+      </c>
+      <c r="I6">
         <v>0</v>
       </c>
-      <c r="H6">
-        <v>7.3</v>
-      </c>
-      <c r="I6">
-        <v>4</v>
-      </c>
       <c r="J6">
-        <v>16.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>50</v>
@@ -2922,25 +2925,25 @@
         <v>24</v>
       </c>
       <c r="D7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>83.33</v>
+        <v>87.5</v>
       </c>
       <c r="G7">
-        <v>16.67</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>12.5</v>
       </c>
     </row>
   </sheetData>
@@ -2950,7 +2953,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2979,39 +2982,39 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>19330051920223</v>
+        <v>19330051920226</v>
       </c>
       <c r="B2" t="s">
         <v>55</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>19330051920223</v>
+        <v>19330051920231</v>
       </c>
       <c r="B3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="D3" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
         <v>46</v>
@@ -3019,881 +3022,241 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>19330051920430</v>
+        <v>19330051920231</v>
       </c>
       <c r="B4" t="s">
         <v>56</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="D4" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>19330051920225</v>
+        <v>19330051920233</v>
       </c>
       <c r="B5" t="s">
         <v>57</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="D5" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>19330051920225</v>
+        <v>19330051920233</v>
       </c>
       <c r="B6" t="s">
         <v>57</v>
       </c>
       <c r="C6" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="D6" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>19330051920226</v>
+        <v>19330051920429</v>
       </c>
       <c r="B7" t="s">
         <v>58</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D7" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>19330051920226</v>
+        <v>19330051920235</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C8" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="D8" t="s">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>19330051920227</v>
+        <v>19330051920237</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C9" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="D9" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>19330051920229</v>
+        <v>19330051420227</v>
       </c>
       <c r="B10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C10" t="s">
         <v>71</v>
       </c>
       <c r="D10" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>19330051920229</v>
+        <v>19330051920404</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D11" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>19330051920230</v>
+        <v>19330051920243</v>
       </c>
       <c r="B12" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="D12" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>19330051920230</v>
+        <v>19330051920243</v>
       </c>
       <c r="B13" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C13" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="D13" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>19330051920231</v>
+        <v>19330051920244</v>
       </c>
       <c r="B14" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C14" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D14" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>19330051920231</v>
+        <v>19330051920245</v>
       </c>
       <c r="B15" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C15" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="D15" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="E15" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>19330051920232</v>
-      </c>
-      <c r="B16" t="s">
-        <v>63</v>
-      </c>
-      <c r="C16" t="s">
-        <v>85</v>
-      </c>
-      <c r="D16" t="s">
-        <v>103</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>19330051920232</v>
-      </c>
-      <c r="B17" t="s">
-        <v>63</v>
-      </c>
-      <c r="C17" t="s">
-        <v>85</v>
-      </c>
-      <c r="D17" t="s">
-        <v>103</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>19330051920233</v>
-      </c>
-      <c r="B18" t="s">
-        <v>64</v>
-      </c>
-      <c r="C18" t="s">
-        <v>86</v>
-      </c>
-      <c r="D18" t="s">
-        <v>104</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>19330051920233</v>
-      </c>
-      <c r="B19" t="s">
-        <v>64</v>
-      </c>
-      <c r="C19" t="s">
-        <v>86</v>
-      </c>
-      <c r="D19" t="s">
-        <v>104</v>
-      </c>
-      <c r="E19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>19330051920233</v>
-      </c>
-      <c r="B20" t="s">
-        <v>64</v>
-      </c>
-      <c r="C20" t="s">
-        <v>86</v>
-      </c>
-      <c r="D20" t="s">
-        <v>104</v>
-      </c>
-      <c r="E20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>19330051920234</v>
-      </c>
-      <c r="B21" t="s">
-        <v>65</v>
-      </c>
-      <c r="C21" t="s">
-        <v>87</v>
-      </c>
-      <c r="D21" t="s">
-        <v>105</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>19330051920429</v>
-      </c>
-      <c r="B22" t="s">
-        <v>66</v>
-      </c>
-      <c r="C22" t="s">
-        <v>88</v>
-      </c>
-      <c r="D22" t="s">
-        <v>106</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>19330051920235</v>
-      </c>
-      <c r="B23" t="s">
-        <v>67</v>
-      </c>
-      <c r="C23" t="s">
-        <v>83</v>
-      </c>
-      <c r="D23" t="s">
-        <v>107</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>19330051920235</v>
-      </c>
-      <c r="B24" t="s">
-        <v>67</v>
-      </c>
-      <c r="C24" t="s">
-        <v>83</v>
-      </c>
-      <c r="D24" t="s">
-        <v>107</v>
-      </c>
-      <c r="E24" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>19330051920236</v>
-      </c>
-      <c r="B25" t="s">
-        <v>68</v>
-      </c>
-      <c r="C25" t="s">
-        <v>66</v>
-      </c>
-      <c r="D25" t="s">
-        <v>108</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>19330051920236</v>
-      </c>
-      <c r="B26" t="s">
-        <v>68</v>
-      </c>
-      <c r="C26" t="s">
-        <v>66</v>
-      </c>
-      <c r="D26" t="s">
-        <v>108</v>
-      </c>
-      <c r="E26" t="s">
-        <v>10</v>
-      </c>
-      <c r="F26" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>19330051920237</v>
-      </c>
-      <c r="B27" t="s">
-        <v>69</v>
-      </c>
-      <c r="C27" t="s">
-        <v>73</v>
-      </c>
-      <c r="D27" t="s">
-        <v>109</v>
-      </c>
-      <c r="E27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>19330051920237</v>
-      </c>
-      <c r="B28" t="s">
-        <v>69</v>
-      </c>
-      <c r="C28" t="s">
-        <v>73</v>
-      </c>
-      <c r="D28" t="s">
-        <v>109</v>
-      </c>
-      <c r="E28" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>19330051920228</v>
-      </c>
-      <c r="B29" t="s">
-        <v>70</v>
-      </c>
-      <c r="C29" t="s">
-        <v>89</v>
-      </c>
-      <c r="D29" t="s">
-        <v>110</v>
-      </c>
-      <c r="E29" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>19330051920228</v>
-      </c>
-      <c r="B30" t="s">
-        <v>70</v>
-      </c>
-      <c r="C30" t="s">
-        <v>89</v>
-      </c>
-      <c r="D30" t="s">
-        <v>110</v>
-      </c>
-      <c r="E30" t="s">
-        <v>10</v>
-      </c>
-      <c r="F30" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>19330051420227</v>
-      </c>
-      <c r="B31" t="s">
-        <v>71</v>
-      </c>
-      <c r="C31" t="s">
-        <v>90</v>
-      </c>
-      <c r="D31" t="s">
-        <v>111</v>
-      </c>
-      <c r="E31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>19330051420227</v>
-      </c>
-      <c r="B32" t="s">
-        <v>71</v>
-      </c>
-      <c r="C32" t="s">
-        <v>90</v>
-      </c>
-      <c r="D32" t="s">
-        <v>111</v>
-      </c>
-      <c r="E32" t="s">
-        <v>10</v>
-      </c>
-      <c r="F32" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>19330051920404</v>
-      </c>
-      <c r="B33" t="s">
-        <v>72</v>
-      </c>
-      <c r="C33" t="s">
-        <v>91</v>
-      </c>
-      <c r="D33" t="s">
-        <v>112</v>
-      </c>
-      <c r="E33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>19330051920404</v>
-      </c>
-      <c r="B34" t="s">
-        <v>72</v>
-      </c>
-      <c r="C34" t="s">
-        <v>91</v>
-      </c>
-      <c r="D34" t="s">
-        <v>112</v>
-      </c>
-      <c r="E34" t="s">
-        <v>10</v>
-      </c>
-      <c r="F34" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>19330051920240</v>
-      </c>
-      <c r="B35" t="s">
-        <v>73</v>
-      </c>
-      <c r="C35" t="s">
-        <v>64</v>
-      </c>
-      <c r="D35" t="s">
-        <v>113</v>
-      </c>
-      <c r="E35" t="s">
-        <v>8</v>
-      </c>
-      <c r="F35" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>19330051920240</v>
-      </c>
-      <c r="B36" t="s">
-        <v>73</v>
-      </c>
-      <c r="C36" t="s">
-        <v>64</v>
-      </c>
-      <c r="D36" t="s">
-        <v>113</v>
-      </c>
-      <c r="E36" t="s">
-        <v>10</v>
-      </c>
-      <c r="F36" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>19330051920239</v>
-      </c>
-      <c r="B37" t="s">
-        <v>74</v>
-      </c>
-      <c r="C37" t="s">
-        <v>92</v>
-      </c>
-      <c r="D37" t="s">
-        <v>114</v>
-      </c>
-      <c r="E37" t="s">
-        <v>8</v>
-      </c>
-      <c r="F37" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>19330051920239</v>
-      </c>
-      <c r="B38" t="s">
-        <v>74</v>
-      </c>
-      <c r="C38" t="s">
-        <v>92</v>
-      </c>
-      <c r="D38" t="s">
-        <v>114</v>
-      </c>
-      <c r="E38" t="s">
-        <v>10</v>
-      </c>
-      <c r="F38" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>19330051920242</v>
-      </c>
-      <c r="B39" t="s">
-        <v>75</v>
-      </c>
-      <c r="C39" t="s">
-        <v>66</v>
-      </c>
-      <c r="D39" t="s">
-        <v>115</v>
-      </c>
-      <c r="E39" t="s">
-        <v>8</v>
-      </c>
-      <c r="F39" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>19330051920242</v>
-      </c>
-      <c r="B40" t="s">
-        <v>75</v>
-      </c>
-      <c r="C40" t="s">
-        <v>66</v>
-      </c>
-      <c r="D40" t="s">
-        <v>115</v>
-      </c>
-      <c r="E40" t="s">
-        <v>10</v>
-      </c>
-      <c r="F40" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>19330051920243</v>
-      </c>
-      <c r="B41" t="s">
-        <v>76</v>
-      </c>
-      <c r="C41" t="s">
-        <v>93</v>
-      </c>
-      <c r="D41" t="s">
-        <v>116</v>
-      </c>
-      <c r="E41" t="s">
-        <v>8</v>
-      </c>
-      <c r="F41" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>19330051920243</v>
-      </c>
-      <c r="B42" t="s">
-        <v>76</v>
-      </c>
-      <c r="C42" t="s">
-        <v>93</v>
-      </c>
-      <c r="D42" t="s">
-        <v>116</v>
-      </c>
-      <c r="E42" t="s">
-        <v>7</v>
-      </c>
-      <c r="F42" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>19330051920243</v>
-      </c>
-      <c r="B43" t="s">
-        <v>76</v>
-      </c>
-      <c r="C43" t="s">
-        <v>93</v>
-      </c>
-      <c r="D43" t="s">
-        <v>116</v>
-      </c>
-      <c r="E43" t="s">
-        <v>10</v>
-      </c>
-      <c r="F43" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>19330051920244</v>
-      </c>
-      <c r="B44" t="s">
-        <v>77</v>
-      </c>
-      <c r="C44" t="s">
-        <v>66</v>
-      </c>
-      <c r="D44" t="s">
-        <v>117</v>
-      </c>
-      <c r="E44" t="s">
-        <v>8</v>
-      </c>
-      <c r="F44" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>19330051920244</v>
-      </c>
-      <c r="B45" t="s">
-        <v>77</v>
-      </c>
-      <c r="C45" t="s">
-        <v>66</v>
-      </c>
-      <c r="D45" t="s">
-        <v>117</v>
-      </c>
-      <c r="E45" t="s">
-        <v>10</v>
-      </c>
-      <c r="F45" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>19330051920245</v>
-      </c>
-      <c r="B46" t="s">
-        <v>78</v>
-      </c>
-      <c r="C46" t="s">
-        <v>94</v>
-      </c>
-      <c r="D46" t="s">
-        <v>118</v>
-      </c>
-      <c r="E46" t="s">
-        <v>8</v>
-      </c>
-      <c r="F46" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>19330051920245</v>
-      </c>
-      <c r="B47" t="s">
-        <v>78</v>
-      </c>
-      <c r="C47" t="s">
-        <v>94</v>
-      </c>
-      <c r="D47" t="s">
-        <v>118</v>
-      </c>
-      <c r="E47" t="s">
-        <v>10</v>
-      </c>
-      <c r="F47" t="s">
         <v>46</v>
       </c>
     </row>
@@ -3930,50 +3293,50 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>19330051920233</v>
+        <v>19330051920231</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>57</v>
       </c>
       <c r="D2" t="s">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920243</v>
+        <v>19330051920233</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="C3" t="s">
-        <v>93</v>
+        <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920223</v>
+        <v>19330051920243</v>
       </c>
       <c r="B4" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D4" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -3981,359 +3344,359 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920225</v>
+        <v>19330051920226</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="D5" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920226</v>
+        <v>19330051920429</v>
       </c>
       <c r="B6" t="s">
         <v>58</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D6" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920229</v>
+        <v>19330051920235</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D7" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920230</v>
+        <v>19330051920237</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="D8" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920231</v>
+        <v>19330051420227</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C9" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="D9" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920232</v>
+        <v>19330051920404</v>
       </c>
       <c r="B10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="D10" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920235</v>
+        <v>19330051920244</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="D11" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920236</v>
+        <v>19330051920245</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C12" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="D12" t="s">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920237</v>
+        <v>19330051920223</v>
       </c>
       <c r="B13" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="C13" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D13" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920228</v>
+        <v>19330051920430</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="C14" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="D14" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051420227</v>
+        <v>19330051920225</v>
       </c>
       <c r="B15" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="C15" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D15" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920404</v>
+        <v>19330051920227</v>
       </c>
       <c r="B16" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="C16" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="D16" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920240</v>
+        <v>19330051920229</v>
       </c>
       <c r="B17" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="C17" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D17" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920239</v>
+        <v>19330051920230</v>
       </c>
       <c r="B18" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="C18" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="D18" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920242</v>
+        <v>19330051920232</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="C19" t="s">
-        <v>66</v>
+        <v>102</v>
       </c>
       <c r="D19" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920244</v>
+        <v>19330051920234</v>
       </c>
       <c r="B20" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="C20" t="s">
-        <v>66</v>
+        <v>103</v>
       </c>
       <c r="D20" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920245</v>
+        <v>19330051920236</v>
       </c>
       <c r="B21" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="C21" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="D21" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920430</v>
+        <v>19330051920228</v>
       </c>
       <c r="B22" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="C22" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="D22" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920227</v>
+        <v>19330051920240</v>
       </c>
       <c r="B23" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="C23" t="s">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="D23" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>19330051920234</v>
+        <v>19330051920239</v>
       </c>
       <c r="B24" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="C24" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="D24" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>19330051920429</v>
+        <v>19330051920242</v>
       </c>
       <c r="B25" t="s">
-        <v>66</v>
+        <v>97</v>
       </c>
       <c r="C25" t="s">
-        <v>88</v>
+        <v>58</v>
       </c>
       <c r="D25" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4343,7 +3706,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4375,68 +3738,68 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920223</v>
+        <v>19330051920227</v>
       </c>
       <c r="B2" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
         <v>45</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920223</v>
+        <v>19330051920227</v>
       </c>
       <c r="B3" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920225</v>
+        <v>19330051920244</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="D4" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -4444,45 +3807,45 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920225</v>
+        <v>19330051920244</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="D5" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920229</v>
+        <v>19330051920429</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D6" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G6">
         <v>-1</v>
@@ -4490,22 +3853,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920229</v>
+        <v>19330051420227</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C7" t="s">
         <v>71</v>
       </c>
       <c r="D7" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G7">
         <v>-1</v>
@@ -4513,22 +3876,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920230</v>
+        <v>19330051920404</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="D8" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G8">
         <v>-1</v>
@@ -4536,461 +3899,47 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920230</v>
+        <v>19330051920240</v>
       </c>
       <c r="B9" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="D9" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920232</v>
+        <v>19330051920245</v>
       </c>
       <c r="B10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D10" t="s">
         <v>85</v>
       </c>
-      <c r="D10" t="s">
-        <v>103</v>
-      </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G10">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>19330051920232</v>
-      </c>
-      <c r="B11" t="s">
-        <v>63</v>
-      </c>
-      <c r="C11" t="s">
-        <v>85</v>
-      </c>
-      <c r="D11" t="s">
-        <v>103</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>46</v>
-      </c>
-      <c r="G11">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>19330051920236</v>
-      </c>
-      <c r="B12" t="s">
-        <v>68</v>
-      </c>
-      <c r="C12" t="s">
-        <v>66</v>
-      </c>
-      <c r="D12" t="s">
-        <v>108</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>45</v>
-      </c>
-      <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>19330051920236</v>
-      </c>
-      <c r="B13" t="s">
-        <v>68</v>
-      </c>
-      <c r="C13" t="s">
-        <v>66</v>
-      </c>
-      <c r="D13" t="s">
-        <v>108</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>46</v>
-      </c>
-      <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>19330051920228</v>
-      </c>
-      <c r="B14" t="s">
-        <v>70</v>
-      </c>
-      <c r="C14" t="s">
-        <v>89</v>
-      </c>
-      <c r="D14" t="s">
-        <v>110</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>45</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>19330051920228</v>
-      </c>
-      <c r="B15" t="s">
-        <v>70</v>
-      </c>
-      <c r="C15" t="s">
-        <v>89</v>
-      </c>
-      <c r="D15" t="s">
-        <v>110</v>
-      </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
-        <v>46</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>19330051420227</v>
-      </c>
-      <c r="B16" t="s">
-        <v>71</v>
-      </c>
-      <c r="C16" t="s">
-        <v>90</v>
-      </c>
-      <c r="D16" t="s">
-        <v>111</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>45</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>19330051420227</v>
-      </c>
-      <c r="B17" t="s">
-        <v>71</v>
-      </c>
-      <c r="C17" t="s">
-        <v>90</v>
-      </c>
-      <c r="D17" t="s">
-        <v>111</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>46</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>19330051920404</v>
-      </c>
-      <c r="B18" t="s">
-        <v>72</v>
-      </c>
-      <c r="C18" t="s">
-        <v>91</v>
-      </c>
-      <c r="D18" t="s">
-        <v>112</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>19330051920404</v>
-      </c>
-      <c r="B19" t="s">
-        <v>72</v>
-      </c>
-      <c r="C19" t="s">
-        <v>91</v>
-      </c>
-      <c r="D19" t="s">
-        <v>112</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" t="s">
-        <v>46</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>19330051920239</v>
-      </c>
-      <c r="B20" t="s">
-        <v>74</v>
-      </c>
-      <c r="C20" t="s">
-        <v>92</v>
-      </c>
-      <c r="D20" t="s">
-        <v>114</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>45</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>19330051920239</v>
-      </c>
-      <c r="B21" t="s">
-        <v>74</v>
-      </c>
-      <c r="C21" t="s">
-        <v>92</v>
-      </c>
-      <c r="D21" t="s">
-        <v>114</v>
-      </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" t="s">
-        <v>46</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>19330051920242</v>
-      </c>
-      <c r="B22" t="s">
-        <v>75</v>
-      </c>
-      <c r="C22" t="s">
-        <v>66</v>
-      </c>
-      <c r="D22" t="s">
-        <v>115</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>45</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>19330051920242</v>
-      </c>
-      <c r="B23" t="s">
-        <v>75</v>
-      </c>
-      <c r="C23" t="s">
-        <v>66</v>
-      </c>
-      <c r="D23" t="s">
-        <v>115</v>
-      </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" t="s">
-        <v>46</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>19330051920245</v>
-      </c>
-      <c r="B24" t="s">
-        <v>78</v>
-      </c>
-      <c r="C24" t="s">
-        <v>94</v>
-      </c>
-      <c r="D24" t="s">
-        <v>118</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>45</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>19330051920245</v>
-      </c>
-      <c r="B25" t="s">
-        <v>78</v>
-      </c>
-      <c r="C25" t="s">
-        <v>94</v>
-      </c>
-      <c r="D25" t="s">
-        <v>118</v>
-      </c>
-      <c r="E25" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" t="s">
-        <v>46</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>19330051920430</v>
-      </c>
-      <c r="B26" t="s">
-        <v>56</v>
-      </c>
-      <c r="C26" t="s">
-        <v>80</v>
-      </c>
-      <c r="D26" t="s">
-        <v>96</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>45</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>19330051920234</v>
-      </c>
-      <c r="B27" t="s">
-        <v>65</v>
-      </c>
-      <c r="C27" t="s">
-        <v>87</v>
-      </c>
-      <c r="D27" t="s">
-        <v>105</v>
-      </c>
-      <c r="E27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" t="s">
-        <v>45</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>19330051920429</v>
-      </c>
-      <c r="B28" t="s">
-        <v>66</v>
-      </c>
-      <c r="C28" t="s">
-        <v>88</v>
-      </c>
-      <c r="D28" t="s">
-        <v>106</v>
-      </c>
-      <c r="E28" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" t="s">
-        <v>45</v>
-      </c>
-      <c r="G28">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/6APM - Estadisticos 20212.xlsx
+++ b/grupos/6APM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="119">
   <si>
     <t>Materia</t>
   </si>
@@ -155,24 +155,24 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Duran Amezcua María Angélica</t>
+  </si>
+  <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
+    <t>Ortega Valle Manuel</t>
+  </si>
+  <si>
     <t>Herrera Serrano Mayra Iliana</t>
   </si>
   <si>
-    <t>Velasco Sánchez David</t>
-  </si>
-  <si>
-    <t>Ochoa Martínez Mayeli</t>
-  </si>
-  <si>
-    <t>Ortega Valle Manuel</t>
-  </si>
-  <si>
     <t>Rodriguez Roman Marisol</t>
   </si>
   <si>
-    <t>Duran Amezcua María Angélica</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -185,22 +185,103 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>GARIBAY</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>HERAS</t>
+  </si>
+  <si>
+    <t>LICEA</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>CALPULALPAN</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>LLAVE</t>
+  </si>
+  <si>
+    <t>MARCOS URIEL</t>
+  </si>
+  <si>
+    <t>URIEL</t>
+  </si>
+  <si>
+    <t>YARELY JACQUELINE</t>
+  </si>
+  <si>
+    <t>CESAR ENRIQUE</t>
+  </si>
+  <si>
+    <t>QADMIEL TAMARA</t>
+  </si>
+  <si>
+    <t>ABDIEL ANTONIO</t>
+  </si>
+  <si>
+    <t>DANIELA JAQUELINE</t>
+  </si>
+  <si>
+    <t>YESUA ISIDRO</t>
+  </si>
+  <si>
+    <t>ALEJO</t>
+  </si>
+  <si>
+    <t>CARDENAS</t>
+  </si>
+  <si>
+    <t>CESPEDES</t>
+  </si>
+  <si>
     <t>CHIPAHUA</t>
   </si>
   <si>
-    <t>GARIBAY</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>HERAS</t>
-  </si>
-  <si>
-    <t>LICEA</t>
+    <t>CHORA</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>ESTRADA</t>
+  </si>
+  <si>
+    <t>GASPAR</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>LADINO</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
   </si>
   <si>
     <t>REYES</t>
@@ -209,28 +290,34 @@
     <t>REYNOSO</t>
   </si>
   <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>VERA</t>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
   </si>
   <si>
     <t>PANZO</t>
   </si>
   <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>CALPULALPAN</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
+    <t>CASTAÑEDA</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>CELICEO</t>
+  </si>
+  <si>
+    <t>HUESCA</t>
   </si>
   <si>
     <t>ANDRADE</t>
@@ -239,133 +326,46 @@
     <t>ALCARAZ</t>
   </si>
   <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>LLAVE</t>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>RAUL ALEJANDRO</t>
+  </si>
+  <si>
+    <t>JOSE LUIS</t>
+  </si>
+  <si>
+    <t>ERICK MANUEL</t>
   </si>
   <si>
     <t>KARLA FABIOLA</t>
   </si>
   <si>
-    <t>MARCOS URIEL</t>
-  </si>
-  <si>
-    <t>URIEL</t>
-  </si>
-  <si>
-    <t>YARELY JACQUELINE</t>
-  </si>
-  <si>
-    <t>CESAR ENRIQUE</t>
-  </si>
-  <si>
-    <t>QADMIEL TAMARA</t>
+    <t>GABRIEL ALEJANDRO</t>
+  </si>
+  <si>
+    <t>IRVING YAHIR</t>
+  </si>
+  <si>
+    <t>BRAULIO VADIR</t>
+  </si>
+  <si>
+    <t>VIANEY</t>
+  </si>
+  <si>
+    <t>PAOLA</t>
+  </si>
+  <si>
+    <t>ZURISADAI</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
   </si>
   <si>
     <t>ALEXANDER</t>
   </si>
   <si>
     <t>RENZO JHOVANI</t>
-  </si>
-  <si>
-    <t>ABDIEL ANTONIO</t>
-  </si>
-  <si>
-    <t>DANIELA JAQUELINE</t>
-  </si>
-  <si>
-    <t>YESUA ISIDRO</t>
-  </si>
-  <si>
-    <t>ALEJO</t>
-  </si>
-  <si>
-    <t>CARDENAS</t>
-  </si>
-  <si>
-    <t>CESPEDES</t>
-  </si>
-  <si>
-    <t>CHORA</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>GASPAR</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>LADINO</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>CASTAÑEDA</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>CELICEO</t>
-  </si>
-  <si>
-    <t>HUESCA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>RAUL ALEJANDRO</t>
-  </si>
-  <si>
-    <t>JOSE LUIS</t>
-  </si>
-  <si>
-    <t>ERICK MANUEL</t>
-  </si>
-  <si>
-    <t>GABRIEL ALEJANDRO</t>
-  </si>
-  <si>
-    <t>IRVING YAHIR</t>
-  </si>
-  <si>
-    <t>BRAULIO VADIR</t>
-  </si>
-  <si>
-    <t>VIANEY</t>
-  </si>
-  <si>
-    <t>PAOLA</t>
-  </si>
-  <si>
-    <t>ZURISADAI</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
   </si>
   <si>
     <t>MARIA DE JESUS</t>
@@ -878,13 +878,13 @@
         <v>6</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K4">
         <v>-1</v>
@@ -893,7 +893,7 @@
         <v>-1</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -914,7 +914,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U4">
         <v>6</v>
@@ -929,7 +929,7 @@
         <v>6</v>
       </c>
       <c r="Y4">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -955,13 +955,13 @@
         <v>6</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K5">
         <v>-1</v>
@@ -970,7 +970,7 @@
         <v>-1</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -991,7 +991,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U5">
         <v>7</v>
@@ -1006,7 +1006,7 @@
         <v>7</v>
       </c>
       <c r="Y5">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1032,13 +1032,13 @@
         <v>6</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K6">
         <v>-1</v>
@@ -1047,7 +1047,7 @@
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1068,10 +1068,10 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V6">
         <v>7</v>
@@ -1083,7 +1083,7 @@
         <v>9</v>
       </c>
       <c r="Y6">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1106,16 +1106,16 @@
         <v>7</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H7">
         <v>-1</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K7">
         <v>-1</v>
@@ -1124,7 +1124,7 @@
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1160,7 +1160,7 @@
         <v>7</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1189,10 +1189,10 @@
         <v>-1</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
         <v>-1</v>
@@ -1201,7 +1201,7 @@
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1237,7 +1237,7 @@
         <v>5</v>
       </c>
       <c r="Y8">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1263,13 +1263,13 @@
         <v>6</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K9">
         <v>-1</v>
@@ -1278,7 +1278,7 @@
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1299,10 +1299,10 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V9">
         <v>9</v>
@@ -1314,7 +1314,7 @@
         <v>6</v>
       </c>
       <c r="Y9">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1340,13 +1340,13 @@
         <v>6</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K10">
         <v>-1</v>
@@ -1355,7 +1355,7 @@
         <v>-1</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1391,7 +1391,7 @@
         <v>8</v>
       </c>
       <c r="Y10">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1417,13 +1417,13 @@
         <v>6</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K11">
         <v>-1</v>
@@ -1432,7 +1432,7 @@
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1456,7 +1456,7 @@
         <v>8</v>
       </c>
       <c r="U11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V11">
         <v>8</v>
@@ -1468,7 +1468,7 @@
         <v>8</v>
       </c>
       <c r="Y11">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1482,7 +1482,7 @@
         <v>5</v>
       </c>
       <c r="D12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E12">
         <v>-1</v>
@@ -1494,13 +1494,13 @@
         <v>6</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I12">
         <v>-1</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K12">
         <v>-1</v>
@@ -1509,7 +1509,7 @@
         <v>-1</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1536,7 +1536,7 @@
         <v>5</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W12">
         <v>-1</v>
@@ -1545,7 +1545,7 @@
         <v>5</v>
       </c>
       <c r="Y12">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1571,13 +1571,13 @@
         <v>6</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K13">
         <v>-1</v>
@@ -1586,7 +1586,7 @@
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1607,10 +1607,10 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V13">
         <v>9</v>
@@ -1622,7 +1622,7 @@
         <v>9</v>
       </c>
       <c r="Y13">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1636,7 +1636,7 @@
         <v>5</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E14">
         <v>-1</v>
@@ -1648,13 +1648,13 @@
         <v>6</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K14">
         <v>-1</v>
@@ -1663,7 +1663,7 @@
         <v>-1</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1684,13 +1684,13 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W14">
         <v>-1</v>
@@ -1699,7 +1699,7 @@
         <v>6</v>
       </c>
       <c r="Y14">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1725,13 +1725,13 @@
         <v>6</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K15">
         <v>-1</v>
@@ -1764,10 +1764,10 @@
         <v>9</v>
       </c>
       <c r="U15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W15">
         <v>8</v>
@@ -1802,10 +1802,10 @@
         <v>8</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J16">
         <v>-1</v>
@@ -1817,7 +1817,7 @@
         <v>-1</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1879,13 +1879,13 @@
         <v>8</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K17">
         <v>-1</v>
@@ -1956,13 +1956,13 @@
         <v>6</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K18">
         <v>-1</v>
@@ -1971,7 +1971,7 @@
         <v>-1</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -1992,10 +1992,10 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V18">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>9</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2039,7 +2039,7 @@
         <v>-1</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K19">
         <v>-1</v>
@@ -2048,7 +2048,7 @@
         <v>-1</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2075,7 +2075,7 @@
         <v>5</v>
       </c>
       <c r="V19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W19">
         <v>-1</v>
@@ -2084,7 +2084,7 @@
         <v>5</v>
       </c>
       <c r="Y19">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2107,16 +2107,16 @@
         <v>8</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K20">
         <v>-1</v>
@@ -2149,10 +2149,10 @@
         <v>8</v>
       </c>
       <c r="U20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W20">
         <v>6</v>
@@ -2161,7 +2161,7 @@
         <v>8</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2184,16 +2184,16 @@
         <v>7</v>
       </c>
       <c r="G21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K21">
         <v>-1</v>
@@ -2202,7 +2202,7 @@
         <v>-1</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2226,7 +2226,7 @@
         <v>9</v>
       </c>
       <c r="U21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V21">
         <v>8</v>
@@ -2238,7 +2238,7 @@
         <v>7</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2264,13 +2264,13 @@
         <v>6</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K22">
         <v>-1</v>
@@ -2279,7 +2279,7 @@
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2303,7 +2303,7 @@
         <v>10</v>
       </c>
       <c r="U22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V22">
         <v>8</v>
@@ -2315,7 +2315,7 @@
         <v>9</v>
       </c>
       <c r="Y22">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2341,13 +2341,13 @@
         <v>6</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K23">
         <v>-1</v>
@@ -2356,7 +2356,7 @@
         <v>-1</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2380,7 +2380,7 @@
         <v>9</v>
       </c>
       <c r="U23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V23">
         <v>8</v>
@@ -2392,7 +2392,7 @@
         <v>8</v>
       </c>
       <c r="Y23">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2418,13 +2418,13 @@
         <v>6</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K24">
         <v>-1</v>
@@ -2433,7 +2433,7 @@
         <v>-1</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2454,10 +2454,10 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V24">
         <v>8</v>
@@ -2469,7 +2469,7 @@
         <v>7</v>
       </c>
       <c r="Y24">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2483,7 +2483,7 @@
         <v>5</v>
       </c>
       <c r="D25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E25">
         <v>-1</v>
@@ -2495,13 +2495,13 @@
         <v>6</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I25">
         <v>-1</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K25">
         <v>-1</v>
@@ -2510,7 +2510,7 @@
         <v>-1</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2537,7 +2537,7 @@
         <v>5</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W25">
         <v>-1</v>
@@ -2546,7 +2546,7 @@
         <v>5</v>
       </c>
       <c r="Y25">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2572,13 +2572,13 @@
         <v>6</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K26">
         <v>-1</v>
@@ -2649,13 +2649,13 @@
         <v>6</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K27">
         <v>-1</v>
@@ -2664,7 +2664,7 @@
         <v>-1</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2688,7 +2688,7 @@
         <v>9</v>
       </c>
       <c r="U27">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V27">
         <v>6</v>
@@ -2700,7 +2700,7 @@
         <v>9</v>
       </c>
       <c r="Y27">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2756,7 +2756,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>45</v>
@@ -2765,19 +2765,19 @@
         <v>24</v>
       </c>
       <c r="D2">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F2">
-        <v>66.67</v>
+        <v>41.67</v>
       </c>
       <c r="G2">
-        <v>33.33</v>
+        <v>58.33</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -2861,30 +2861,30 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>83.33</v>
+        <v>75</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>20.83</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>16.67</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>49</v>
@@ -2893,19 +2893,19 @@
         <v>24</v>
       </c>
       <c r="D6">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>83.33</v>
+        <v>75</v>
       </c>
       <c r="G6">
-        <v>16.67</v>
+        <v>25</v>
       </c>
       <c r="H6">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -2916,7 +2916,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>50</v>
@@ -2928,22 +2928,22 @@
         <v>21</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F7">
         <v>87.5</v>
       </c>
       <c r="G7">
+        <v>12.5</v>
+      </c>
+      <c r="H7">
+        <v>7.4</v>
+      </c>
+      <c r="I7">
         <v>0</v>
       </c>
-      <c r="H7">
-        <v>6.2</v>
-      </c>
-      <c r="I7">
-        <v>3</v>
-      </c>
       <c r="J7">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2953,7 +2953,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2982,36 +2982,36 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>19330051920226</v>
+        <v>19330051920231</v>
       </c>
       <c r="B2" t="s">
         <v>55</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="D2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>19330051920231</v>
+        <v>19330051920233</v>
       </c>
       <c r="B3" t="s">
         <v>56</v>
       </c>
       <c r="C3" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D3" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -3022,76 +3022,76 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>19330051920231</v>
+        <v>19330051920429</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D4" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>19330051920233</v>
+        <v>19330051920235</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D5" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>19330051920233</v>
+        <v>19330051920237</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D6" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>19330051920429</v>
+        <v>19330051920243</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D7" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -3102,161 +3102,41 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>19330051920235</v>
+        <v>19330051920244</v>
       </c>
       <c r="B8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="D8" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>19330051920237</v>
+        <v>19330051920245</v>
       </c>
       <c r="B9" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D9" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>19330051420227</v>
-      </c>
-      <c r="B10" t="s">
-        <v>61</v>
-      </c>
-      <c r="C10" t="s">
-        <v>71</v>
-      </c>
-      <c r="D10" t="s">
-        <v>81</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>19330051920404</v>
-      </c>
-      <c r="B11" t="s">
-        <v>62</v>
-      </c>
-      <c r="C11" t="s">
-        <v>72</v>
-      </c>
-      <c r="D11" t="s">
-        <v>82</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>19330051920243</v>
-      </c>
-      <c r="B12" t="s">
-        <v>63</v>
-      </c>
-      <c r="C12" t="s">
-        <v>73</v>
-      </c>
-      <c r="D12" t="s">
-        <v>83</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>19330051920243</v>
-      </c>
-      <c r="B13" t="s">
-        <v>63</v>
-      </c>
-      <c r="C13" t="s">
-        <v>73</v>
-      </c>
-      <c r="D13" t="s">
-        <v>83</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>19330051920244</v>
-      </c>
-      <c r="B14" t="s">
-        <v>64</v>
-      </c>
-      <c r="C14" t="s">
-        <v>58</v>
-      </c>
-      <c r="D14" t="s">
-        <v>84</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>19330051920245</v>
-      </c>
-      <c r="B15" t="s">
-        <v>65</v>
-      </c>
-      <c r="C15" t="s">
-        <v>74</v>
-      </c>
-      <c r="D15" t="s">
-        <v>85</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
         <v>46</v>
       </c>
     </row>
@@ -3296,16 +3176,16 @@
         <v>19330051920231</v>
       </c>
       <c r="B2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" t="s">
         <v>56</v>
       </c>
-      <c r="C2" t="s">
-        <v>57</v>
-      </c>
       <c r="D2" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3313,47 +3193,47 @@
         <v>19330051920233</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D3" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920243</v>
+        <v>19330051920429</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D4" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920226</v>
+        <v>19330051920235</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -3361,16 +3241,16 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920429</v>
+        <v>19330051920237</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D6" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -3378,16 +3258,16 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920235</v>
+        <v>19330051920243</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D7" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -3395,16 +3275,16 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920237</v>
+        <v>19330051920244</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C8" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="D8" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -3412,16 +3292,16 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051420227</v>
+        <v>19330051920245</v>
       </c>
       <c r="B9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D9" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -3429,64 +3309,64 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920404</v>
+        <v>19330051920223</v>
       </c>
       <c r="B10" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="D10" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920244</v>
+        <v>19330051920430</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="D11" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920245</v>
+        <v>19330051920225</v>
       </c>
       <c r="B12" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="C12" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="D12" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920223</v>
+        <v>19330051920226</v>
       </c>
       <c r="B13" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C13" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D13" t="s">
         <v>106</v>
@@ -3497,13 +3377,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920430</v>
+        <v>19330051920227</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C14" t="s">
-        <v>99</v>
+        <v>65</v>
       </c>
       <c r="D14" t="s">
         <v>107</v>
@@ -3514,13 +3394,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920225</v>
+        <v>19330051920229</v>
       </c>
       <c r="B15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C15" t="s">
         <v>88</v>
-      </c>
-      <c r="C15" t="s">
-        <v>100</v>
       </c>
       <c r="D15" t="s">
         <v>108</v>
@@ -3531,13 +3411,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920227</v>
+        <v>19330051920230</v>
       </c>
       <c r="B16" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C16" t="s">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="D16" t="s">
         <v>109</v>
@@ -3548,13 +3428,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920229</v>
+        <v>19330051920232</v>
       </c>
       <c r="B17" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C17" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="D17" t="s">
         <v>110</v>
@@ -3565,13 +3445,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920230</v>
+        <v>19330051920234</v>
       </c>
       <c r="B18" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C18" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D18" t="s">
         <v>111</v>
@@ -3582,13 +3462,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920232</v>
+        <v>19330051920236</v>
       </c>
       <c r="B19" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C19" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="D19" t="s">
         <v>112</v>
@@ -3599,13 +3479,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920234</v>
+        <v>19330051920228</v>
       </c>
       <c r="B20" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C20" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D20" t="s">
         <v>113</v>
@@ -3616,13 +3496,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920236</v>
+        <v>19330051420227</v>
       </c>
       <c r="B21" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C21" t="s">
-        <v>58</v>
+        <v>100</v>
       </c>
       <c r="D21" t="s">
         <v>114</v>
@@ -3633,13 +3513,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920228</v>
+        <v>19330051920404</v>
       </c>
       <c r="B22" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C22" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D22" t="s">
         <v>115</v>
@@ -3653,10 +3533,10 @@
         <v>19330051920240</v>
       </c>
       <c r="B23" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C23" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D23" t="s">
         <v>116</v>
@@ -3670,10 +3550,10 @@
         <v>19330051920239</v>
       </c>
       <c r="B24" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C24" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D24" t="s">
         <v>117</v>
@@ -3687,10 +3567,10 @@
         <v>19330051920242</v>
       </c>
       <c r="B25" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C25" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D25" t="s">
         <v>118</v>
@@ -3706,7 +3586,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3738,22 +3618,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920227</v>
+        <v>19330051420227</v>
       </c>
       <c r="B2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="D2" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -3761,22 +3641,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920227</v>
+        <v>19330051420227</v>
       </c>
       <c r="B3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="D3" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -3787,13 +3667,13 @@
         <v>19330051920244</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D4" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -3810,13 +3690,13 @@
         <v>19330051920244</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D5" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -3830,88 +3710,88 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920429</v>
+        <v>19330051920223</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="D6" t="s">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051420227</v>
+        <v>19330051920430</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="D7" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920404</v>
+        <v>19330051920225</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920240</v>
+        <v>19330051920230</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="C9" t="s">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="D9" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
         <v>45</v>
@@ -3922,16 +3802,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920245</v>
+        <v>19330051920429</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C10" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="D10" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -3940,6 +3820,98 @@
         <v>46</v>
       </c>
       <c r="G10">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>19330051920236</v>
+      </c>
+      <c r="B11" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" t="s">
+        <v>112</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>45</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>19330051920239</v>
+      </c>
+      <c r="B12" t="s">
+        <v>90</v>
+      </c>
+      <c r="C12" t="s">
+        <v>102</v>
+      </c>
+      <c r="D12" t="s">
+        <v>117</v>
+      </c>
+      <c r="E12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>19330051920242</v>
+      </c>
+      <c r="B13" t="s">
+        <v>91</v>
+      </c>
+      <c r="C13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" t="s">
+        <v>118</v>
+      </c>
+      <c r="E13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" t="s">
+        <v>45</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>19330051920245</v>
+      </c>
+      <c r="B14" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" t="s">
+        <v>76</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>46</v>
+      </c>
+      <c r="G14">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/6APM - Estadisticos 20212.xlsx
+++ b/grupos/6APM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="119">
   <si>
     <t>Materia</t>
   </si>
@@ -158,21 +158,21 @@
     <t>Duran Amezcua María Angélica</t>
   </si>
   <si>
+    <t>Ortega Valle Manuel</t>
+  </si>
+  <si>
+    <t>Herrera Serrano Mayra Iliana</t>
+  </si>
+  <si>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
+    <t>Rodriguez Roman Marisol</t>
+  </si>
+  <si>
     <t>Velasco Sánchez David</t>
   </si>
   <si>
-    <t>Ochoa Martínez Mayeli</t>
-  </si>
-  <si>
-    <t>Ortega Valle Manuel</t>
-  </si>
-  <si>
-    <t>Herrera Serrano Mayra Iliana</t>
-  </si>
-  <si>
-    <t>Rodriguez Roman Marisol</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -185,21 +185,75 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>HERAS</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>CESAR ENRIQUE</t>
+  </si>
+  <si>
+    <t>ALEJO</t>
+  </si>
+  <si>
+    <t>CARDENAS</t>
+  </si>
+  <si>
+    <t>CESPEDES</t>
+  </si>
+  <si>
+    <t>CHIPAHUA</t>
+  </si>
+  <si>
+    <t>CHORA</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>ESTRADA</t>
+  </si>
+  <si>
     <t>GARIBAY</t>
   </si>
   <si>
+    <t>GASPAR</t>
+  </si>
+  <si>
     <t>GOMEZ</t>
   </si>
   <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>HERAS</t>
+    <t>LADINO</t>
   </si>
   <si>
     <t>LICEA</t>
   </si>
   <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>REYNOSO</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>SERRANO</t>
   </si>
   <si>
@@ -209,16 +263,43 @@
     <t>VERA</t>
   </si>
   <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>PANZO</t>
+  </si>
+  <si>
+    <t>CASTAÑEDA</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
     <t>MORALES</t>
   </si>
   <si>
+    <t>CELICEO</t>
+  </si>
+  <si>
     <t>CALPULALPAN</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
+    <t>HUESCA</t>
+  </si>
+  <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>ALCARAZ</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
   </si>
   <si>
     <t>HUERTA</t>
@@ -227,21 +308,66 @@
     <t>LLAVE</t>
   </si>
   <si>
+    <t>RAUL ALEJANDRO</t>
+  </si>
+  <si>
+    <t>JOSE LUIS</t>
+  </si>
+  <si>
+    <t>ERICK MANUEL</t>
+  </si>
+  <si>
+    <t>KARLA FABIOLA</t>
+  </si>
+  <si>
+    <t>GABRIEL ALEJANDRO</t>
+  </si>
+  <si>
+    <t>IRVING YAHIR</t>
+  </si>
+  <si>
+    <t>BRAULIO VADIR</t>
+  </si>
+  <si>
     <t>MARCOS URIEL</t>
   </si>
   <si>
+    <t>VIANEY</t>
+  </si>
+  <si>
     <t>URIEL</t>
   </si>
   <si>
+    <t>PAOLA</t>
+  </si>
+  <si>
     <t>YARELY JACQUELINE</t>
   </si>
   <si>
-    <t>CESAR ENRIQUE</t>
+    <t>ZURISADAI</t>
   </si>
   <si>
     <t>QADMIEL TAMARA</t>
   </si>
   <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>ALEXANDER</t>
+  </si>
+  <si>
+    <t>RENZO JHOVANI</t>
+  </si>
+  <si>
+    <t>MARIA DE JESUS</t>
+  </si>
+  <si>
+    <t>NADYA GUADALUPE</t>
+  </si>
+  <si>
+    <t>ANGEL EDUARDO</t>
+  </si>
+  <si>
     <t>ABDIEL ANTONIO</t>
   </si>
   <si>
@@ -249,132 +375,6 @@
   </si>
   <si>
     <t>YESUA ISIDRO</t>
-  </si>
-  <si>
-    <t>ALEJO</t>
-  </si>
-  <si>
-    <t>CARDENAS</t>
-  </si>
-  <si>
-    <t>CESPEDES</t>
-  </si>
-  <si>
-    <t>CHIPAHUA</t>
-  </si>
-  <si>
-    <t>CHORA</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>GASPAR</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>LADINO</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>REYNOSO</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>PANZO</t>
-  </si>
-  <si>
-    <t>CASTAÑEDA</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>CELICEO</t>
-  </si>
-  <si>
-    <t>HUESCA</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>ALCARAZ</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>RAUL ALEJANDRO</t>
-  </si>
-  <si>
-    <t>JOSE LUIS</t>
-  </si>
-  <si>
-    <t>ERICK MANUEL</t>
-  </si>
-  <si>
-    <t>KARLA FABIOLA</t>
-  </si>
-  <si>
-    <t>GABRIEL ALEJANDRO</t>
-  </si>
-  <si>
-    <t>IRVING YAHIR</t>
-  </si>
-  <si>
-    <t>BRAULIO VADIR</t>
-  </si>
-  <si>
-    <t>VIANEY</t>
-  </si>
-  <si>
-    <t>PAOLA</t>
-  </si>
-  <si>
-    <t>ZURISADAI</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>ALEXANDER</t>
-  </si>
-  <si>
-    <t>RENZO JHOVANI</t>
-  </si>
-  <si>
-    <t>MARIA DE JESUS</t>
-  </si>
-  <si>
-    <t>NADYA GUADALUPE</t>
-  </si>
-  <si>
-    <t>ANGEL EDUARDO</t>
   </si>
 </sst>
 </file>
@@ -887,10 +887,10 @@
         <v>8</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M4">
         <v>5</v>
@@ -923,7 +923,7 @@
         <v>8</v>
       </c>
       <c r="W4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X4">
         <v>6</v>
@@ -964,10 +964,10 @@
         <v>6</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M5">
         <v>5</v>
@@ -1000,10 +1000,10 @@
         <v>7</v>
       </c>
       <c r="W5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y5">
         <v>5</v>
@@ -1041,10 +1041,10 @@
         <v>7</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M6">
         <v>5</v>
@@ -1118,10 +1118,10 @@
         <v>6</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M7">
         <v>5</v>
@@ -1154,10 +1154,10 @@
         <v>6</v>
       </c>
       <c r="W7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y7">
         <v>5</v>
@@ -1195,10 +1195,10 @@
         <v>8</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
         <v>5</v>
@@ -1231,10 +1231,10 @@
         <v>8</v>
       </c>
       <c r="W8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y8">
         <v>5</v>
@@ -1272,10 +1272,10 @@
         <v>8</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M9">
         <v>7</v>
@@ -1308,10 +1308,10 @@
         <v>9</v>
       </c>
       <c r="W9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y9">
         <v>7</v>
@@ -1349,10 +1349,10 @@
         <v>8</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M10">
         <v>7</v>
@@ -1388,7 +1388,7 @@
         <v>9</v>
       </c>
       <c r="X10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y10">
         <v>7</v>
@@ -1426,10 +1426,10 @@
         <v>8</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M11">
         <v>5</v>
@@ -1462,10 +1462,10 @@
         <v>8</v>
       </c>
       <c r="W11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y11">
         <v>5</v>
@@ -1485,7 +1485,7 @@
         <v>6</v>
       </c>
       <c r="E12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -1506,7 +1506,7 @@
         <v>-1</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M12">
         <v>5</v>
@@ -1539,7 +1539,7 @@
         <v>5</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X12">
         <v>5</v>
@@ -1580,10 +1580,10 @@
         <v>9</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M13">
         <v>8</v>
@@ -1639,7 +1639,7 @@
         <v>6</v>
       </c>
       <c r="E14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F14">
         <v>6</v>
@@ -1657,10 +1657,10 @@
         <v>5</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M14">
         <v>5</v>
@@ -1693,7 +1693,7 @@
         <v>5</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X14">
         <v>6</v>
@@ -1734,10 +1734,10 @@
         <v>7</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M15">
         <v>-1</v>
@@ -1770,7 +1770,7 @@
         <v>7</v>
       </c>
       <c r="W15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X15">
         <v>10</v>
@@ -1811,10 +1811,10 @@
         <v>-1</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M16">
         <v>8</v>
@@ -1870,7 +1870,7 @@
         <v>6</v>
       </c>
       <c r="E17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F17">
         <v>6</v>
@@ -1888,10 +1888,10 @@
         <v>6</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M17">
         <v>-1</v>
@@ -1924,10 +1924,10 @@
         <v>6</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y17">
         <v>8</v>
@@ -1965,10 +1965,10 @@
         <v>8</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M18">
         <v>5</v>
@@ -2004,7 +2004,7 @@
         <v>10</v>
       </c>
       <c r="X18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y18">
         <v>5</v>
@@ -2024,7 +2024,7 @@
         <v>6</v>
       </c>
       <c r="E19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F19">
         <v>5</v>
@@ -2045,7 +2045,7 @@
         <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M19">
         <v>5</v>
@@ -2078,7 +2078,7 @@
         <v>5</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X19">
         <v>5</v>
@@ -2119,10 +2119,10 @@
         <v>5</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M20">
         <v>-1</v>
@@ -2155,10 +2155,10 @@
         <v>5</v>
       </c>
       <c r="W20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y20">
         <v>5</v>
@@ -2196,10 +2196,10 @@
         <v>8</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M21">
         <v>8</v>
@@ -2235,7 +2235,7 @@
         <v>9</v>
       </c>
       <c r="X21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y21">
         <v>8</v>
@@ -2273,10 +2273,10 @@
         <v>7</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M22">
         <v>5</v>
@@ -2350,10 +2350,10 @@
         <v>8</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M23">
         <v>10</v>
@@ -2386,7 +2386,7 @@
         <v>8</v>
       </c>
       <c r="W23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X23">
         <v>8</v>
@@ -2427,10 +2427,10 @@
         <v>8</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M24">
         <v>5</v>
@@ -2463,10 +2463,10 @@
         <v>8</v>
       </c>
       <c r="W24">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y24">
         <v>5</v>
@@ -2486,7 +2486,7 @@
         <v>6</v>
       </c>
       <c r="E25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F25">
         <v>5</v>
@@ -2498,16 +2498,16 @@
         <v>6</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J25">
         <v>5</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M25">
         <v>5</v>
@@ -2540,10 +2540,10 @@
         <v>5</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y25">
         <v>5</v>
@@ -2563,7 +2563,7 @@
         <v>6</v>
       </c>
       <c r="E26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F26">
         <v>5</v>
@@ -2581,10 +2581,10 @@
         <v>6</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M26">
         <v>-1</v>
@@ -2617,7 +2617,7 @@
         <v>6</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X26">
         <v>5</v>
@@ -2640,7 +2640,7 @@
         <v>6</v>
       </c>
       <c r="E27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F27">
         <v>9</v>
@@ -2658,10 +2658,10 @@
         <v>6</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M27">
         <v>8</v>
@@ -2694,7 +2694,7 @@
         <v>6</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X27">
         <v>9</v>
@@ -2788,7 +2788,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>46</v>
@@ -2797,30 +2797,30 @@
         <v>24</v>
       </c>
       <c r="D3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>70.83</v>
+        <v>75</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>20.83</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>7</v>
       </c>
       <c r="I3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>29.17</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>47</v>
@@ -2841,7 +2841,7 @@
         <v>25</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -2852,7 +2852,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>48</v>
@@ -2861,30 +2861,30 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>75</v>
+        <v>83.33</v>
       </c>
       <c r="G5">
-        <v>20.83</v>
+        <v>16.67</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>4.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>49</v>
@@ -2893,19 +2893,19 @@
         <v>24</v>
       </c>
       <c r="D6">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="G6">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="H6">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -2916,7 +2916,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>50</v>
@@ -2925,19 +2925,19 @@
         <v>24</v>
       </c>
       <c r="D7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>87.5</v>
+        <v>91.67</v>
       </c>
       <c r="G7">
-        <v>12.5</v>
+        <v>8.33</v>
       </c>
       <c r="H7">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -2953,7 +2953,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2982,7 +2982,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>19330051920231</v>
+        <v>19330051920235</v>
       </c>
       <c r="B2" t="s">
         <v>55</v>
@@ -2991,152 +2991,12 @@
         <v>56</v>
       </c>
       <c r="D2" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>19330051920233</v>
-      </c>
-      <c r="B3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>19330051920429</v>
-      </c>
-      <c r="B4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D4" t="s">
-        <v>71</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>19330051920235</v>
-      </c>
-      <c r="B5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D5" t="s">
-        <v>72</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>19330051920237</v>
-      </c>
-      <c r="B6" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D6" t="s">
-        <v>73</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>19330051920243</v>
-      </c>
-      <c r="B7" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" t="s">
-        <v>67</v>
-      </c>
-      <c r="D7" t="s">
-        <v>74</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>19330051920244</v>
-      </c>
-      <c r="B8" t="s">
-        <v>61</v>
-      </c>
-      <c r="C8" t="s">
-        <v>57</v>
-      </c>
-      <c r="D8" t="s">
-        <v>75</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>19330051920245</v>
-      </c>
-      <c r="B9" t="s">
-        <v>62</v>
-      </c>
-      <c r="C9" t="s">
-        <v>68</v>
-      </c>
-      <c r="D9" t="s">
-        <v>76</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
         <v>46</v>
       </c>
     </row>
@@ -3173,7 +3033,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>19330051920231</v>
+        <v>19330051920235</v>
       </c>
       <c r="B2" t="s">
         <v>55</v>
@@ -3182,7 +3042,7 @@
         <v>56</v>
       </c>
       <c r="D2" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -3190,132 +3050,132 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920233</v>
+        <v>19330051920223</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920429</v>
+        <v>19330051920430</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920235</v>
+        <v>19330051920225</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920237</v>
+        <v>19330051920226</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C6" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="D6" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920243</v>
+        <v>19330051920227</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C7" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="D7" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920244</v>
+        <v>19330051920229</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="D8" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920245</v>
+        <v>19330051920230</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920223</v>
+        <v>19330051920231</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="C10" t="s">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="D10" t="s">
         <v>103</v>
@@ -3326,13 +3186,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920430</v>
+        <v>19330051920232</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C11" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="D11" t="s">
         <v>104</v>
@@ -3343,13 +3203,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920225</v>
+        <v>19330051920233</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="C12" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="D12" t="s">
         <v>105</v>
@@ -3360,13 +3220,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920226</v>
+        <v>19330051920234</v>
       </c>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="C13" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="D13" t="s">
         <v>106</v>
@@ -3377,13 +3237,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920227</v>
+        <v>19330051920429</v>
       </c>
       <c r="B14" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="C14" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="D14" t="s">
         <v>107</v>
@@ -3394,13 +3254,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920229</v>
+        <v>19330051920236</v>
       </c>
       <c r="B15" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="C15" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="D15" t="s">
         <v>108</v>
@@ -3411,13 +3271,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920230</v>
+        <v>19330051920237</v>
       </c>
       <c r="B16" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C16" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="D16" t="s">
         <v>109</v>
@@ -3428,13 +3288,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920232</v>
+        <v>19330051920228</v>
       </c>
       <c r="B17" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C17" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="D17" t="s">
         <v>110</v>
@@ -3445,13 +3305,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920234</v>
+        <v>19330051420227</v>
       </c>
       <c r="B18" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="C18" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="D18" t="s">
         <v>111</v>
@@ -3462,13 +3322,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920236</v>
+        <v>19330051920404</v>
       </c>
       <c r="B19" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="C19" t="s">
-        <v>57</v>
+        <v>92</v>
       </c>
       <c r="D19" t="s">
         <v>112</v>
@@ -3479,13 +3339,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920228</v>
+        <v>19330051920240</v>
       </c>
       <c r="B20" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="C20" t="s">
-        <v>99</v>
+        <v>67</v>
       </c>
       <c r="D20" t="s">
         <v>113</v>
@@ -3496,13 +3356,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051420227</v>
+        <v>19330051920239</v>
       </c>
       <c r="B21" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="C21" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="D21" t="s">
         <v>114</v>
@@ -3513,13 +3373,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920404</v>
+        <v>19330051920242</v>
       </c>
       <c r="B22" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="C22" t="s">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="D22" t="s">
         <v>115</v>
@@ -3530,13 +3390,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920240</v>
+        <v>19330051920243</v>
       </c>
       <c r="B23" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="C23" t="s">
-        <v>56</v>
+        <v>94</v>
       </c>
       <c r="D23" t="s">
         <v>116</v>
@@ -3547,13 +3407,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>19330051920239</v>
+        <v>19330051920244</v>
       </c>
       <c r="B24" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="C24" t="s">
-        <v>102</v>
+        <v>69</v>
       </c>
       <c r="D24" t="s">
         <v>117</v>
@@ -3564,13 +3424,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>19330051920242</v>
+        <v>19330051920245</v>
       </c>
       <c r="B25" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="C25" t="s">
-        <v>57</v>
+        <v>95</v>
       </c>
       <c r="D25" t="s">
         <v>118</v>
@@ -3586,7 +3446,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3618,22 +3478,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051420227</v>
+        <v>19330051920227</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" t="s">
         <v>100</v>
       </c>
-      <c r="D2" t="s">
-        <v>114</v>
-      </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -3641,16 +3501,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051420227</v>
+        <v>19330051920227</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="C3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" t="s">
         <v>100</v>
-      </c>
-      <c r="D3" t="s">
-        <v>114</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -3664,45 +3524,45 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920244</v>
+        <v>19330051920233</v>
       </c>
       <c r="B4" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="D4" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
         <v>46</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920244</v>
+        <v>19330051920233</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="D5" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -3710,22 +3570,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920223</v>
+        <v>19330051420227</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -3733,16 +3593,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920430</v>
+        <v>19330051420227</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -3756,16 +3616,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920225</v>
+        <v>19330051920223</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="D8" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
@@ -3779,16 +3639,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920230</v>
+        <v>19330051920430</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="C9" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -3802,39 +3662,39 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920429</v>
+        <v>19330051920225</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C10" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="D10" t="s">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920236</v>
+        <v>19330051920230</v>
       </c>
       <c r="B11" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="D11" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -3848,16 +3708,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920239</v>
+        <v>19330051920236</v>
       </c>
       <c r="B12" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="C12" t="s">
-        <v>102</v>
+        <v>69</v>
       </c>
       <c r="D12" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
@@ -3871,16 +3731,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920242</v>
+        <v>19330051920239</v>
       </c>
       <c r="B13" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="C13" t="s">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="D13" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -3894,25 +3754,48 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19330051920245</v>
+        <v>19330051920242</v>
       </c>
       <c r="B14" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="C14" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D14" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="E14" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>19330051920244</v>
+      </c>
+      <c r="B15" t="s">
+        <v>79</v>
+      </c>
+      <c r="C15" t="s">
+        <v>69</v>
+      </c>
+      <c r="D15" t="s">
+        <v>117</v>
+      </c>
+      <c r="E15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" t="s">
+        <v>48</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/6APM - Estadisticos 20212.xlsx
+++ b/grupos/6APM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="119">
   <si>
     <t>Materia</t>
   </si>
@@ -158,21 +158,21 @@
     <t>Duran Amezcua María Angélica</t>
   </si>
   <si>
+    <t>Herrera Serrano Mayra Iliana</t>
+  </si>
+  <si>
+    <t>Rodriguez Roman Marisol</t>
+  </si>
+  <si>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
     <t>Ortega Valle Manuel</t>
   </si>
   <si>
-    <t>Herrera Serrano Mayra Iliana</t>
-  </si>
-  <si>
-    <t>Ochoa Martínez Mayeli</t>
-  </si>
-  <si>
-    <t>Rodriguez Roman Marisol</t>
-  </si>
-  <si>
-    <t>Velasco Sánchez David</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -185,163 +185,163 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ALEJO</t>
+  </si>
+  <si>
+    <t>CARDENAS</t>
+  </si>
+  <si>
+    <t>CESPEDES</t>
+  </si>
+  <si>
+    <t>CHIPAHUA</t>
+  </si>
+  <si>
+    <t>CHORA</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>ESTRADA</t>
+  </si>
+  <si>
+    <t>GARIBAY</t>
+  </si>
+  <si>
+    <t>GASPAR</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>HERAS</t>
   </si>
   <si>
+    <t>LADINO</t>
+  </si>
+  <si>
+    <t>LICEA</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>REYNOSO</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>PANZO</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>CASTAÑEDA</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>CELICEO</t>
+  </si>
+  <si>
+    <t>CALPULALPAN</t>
+  </si>
+  <si>
+    <t>HUESCA</t>
+  </si>
+  <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>ALCARAZ</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>LLAVE</t>
+  </si>
+  <si>
+    <t>RAUL ALEJANDRO</t>
+  </si>
+  <si>
+    <t>JOSE LUIS</t>
+  </si>
+  <si>
+    <t>ERICK MANUEL</t>
+  </si>
+  <si>
+    <t>KARLA FABIOLA</t>
+  </si>
+  <si>
+    <t>GABRIEL ALEJANDRO</t>
+  </si>
+  <si>
+    <t>IRVING YAHIR</t>
+  </si>
+  <si>
+    <t>BRAULIO VADIR</t>
+  </si>
+  <si>
+    <t>MARCOS URIEL</t>
+  </si>
+  <si>
+    <t>VIANEY</t>
+  </si>
+  <si>
+    <t>URIEL</t>
+  </si>
+  <si>
+    <t>PAOLA</t>
+  </si>
+  <si>
+    <t>YARELY JACQUELINE</t>
+  </si>
+  <si>
     <t>CESAR ENRIQUE</t>
-  </si>
-  <si>
-    <t>ALEJO</t>
-  </si>
-  <si>
-    <t>CARDENAS</t>
-  </si>
-  <si>
-    <t>CESPEDES</t>
-  </si>
-  <si>
-    <t>CHIPAHUA</t>
-  </si>
-  <si>
-    <t>CHORA</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>GARIBAY</t>
-  </si>
-  <si>
-    <t>GASPAR</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LADINO</t>
-  </si>
-  <si>
-    <t>LICEA</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>REYNOSO</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>PANZO</t>
-  </si>
-  <si>
-    <t>CASTAÑEDA</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>CELICEO</t>
-  </si>
-  <si>
-    <t>CALPULALPAN</t>
-  </si>
-  <si>
-    <t>HUESCA</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>ALCARAZ</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>LLAVE</t>
-  </si>
-  <si>
-    <t>RAUL ALEJANDRO</t>
-  </si>
-  <si>
-    <t>JOSE LUIS</t>
-  </si>
-  <si>
-    <t>ERICK MANUEL</t>
-  </si>
-  <si>
-    <t>KARLA FABIOLA</t>
-  </si>
-  <si>
-    <t>GABRIEL ALEJANDRO</t>
-  </si>
-  <si>
-    <t>IRVING YAHIR</t>
-  </si>
-  <si>
-    <t>BRAULIO VADIR</t>
-  </si>
-  <si>
-    <t>MARCOS URIEL</t>
-  </si>
-  <si>
-    <t>VIANEY</t>
-  </si>
-  <si>
-    <t>URIEL</t>
-  </si>
-  <si>
-    <t>PAOLA</t>
-  </si>
-  <si>
-    <t>YARELY JACQUELINE</t>
   </si>
   <si>
     <t>ZURISADAI</t>
@@ -902,13 +902,13 @@
         <v>-1</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S4">
         <v>-1</v>
@@ -920,13 +920,13 @@
         <v>6</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W4">
         <v>8</v>
       </c>
       <c r="X4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y4">
         <v>5</v>
@@ -979,13 +979,13 @@
         <v>-1</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S5">
         <v>-1</v>
@@ -1000,10 +1000,10 @@
         <v>7</v>
       </c>
       <c r="W5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y5">
         <v>5</v>
@@ -1056,13 +1056,13 @@
         <v>-1</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S6">
         <v>-1</v>
@@ -1133,13 +1133,13 @@
         <v>-1</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S7">
         <v>-1</v>
@@ -1154,10 +1154,10 @@
         <v>6</v>
       </c>
       <c r="W7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y7">
         <v>5</v>
@@ -1210,13 +1210,13 @@
         <v>-1</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S8">
         <v>-1</v>
@@ -1231,7 +1231,7 @@
         <v>8</v>
       </c>
       <c r="W8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X8">
         <v>7</v>
@@ -1287,13 +1287,13 @@
         <v>-1</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S9">
         <v>-1</v>
@@ -1364,13 +1364,13 @@
         <v>-1</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S10">
         <v>-1</v>
@@ -1385,10 +1385,10 @@
         <v>8</v>
       </c>
       <c r="W10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y10">
         <v>7</v>
@@ -1441,13 +1441,13 @@
         <v>-1</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S11">
         <v>-1</v>
@@ -1462,10 +1462,10 @@
         <v>8</v>
       </c>
       <c r="W11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y11">
         <v>5</v>
@@ -1497,13 +1497,13 @@
         <v>6</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J12">
         <v>5</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L12">
         <v>5</v>
@@ -1518,13 +1518,13 @@
         <v>-1</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S12">
         <v>-1</v>
@@ -1595,13 +1595,13 @@
         <v>-1</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S13">
         <v>-1</v>
@@ -1672,13 +1672,13 @@
         <v>-1</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S14">
         <v>-1</v>
@@ -1690,13 +1690,13 @@
         <v>6</v>
       </c>
       <c r="V14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W14">
         <v>7</v>
       </c>
       <c r="X14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y14">
         <v>5</v>
@@ -1749,13 +1749,13 @@
         <v>-1</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S15">
         <v>-1</v>
@@ -1770,7 +1770,7 @@
         <v>7</v>
       </c>
       <c r="W15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X15">
         <v>10</v>
@@ -1790,7 +1790,7 @@
         <v>5</v>
       </c>
       <c r="D16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E16">
         <v>6</v>
@@ -1808,7 +1808,7 @@
         <v>6</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K16">
         <v>6</v>
@@ -1826,13 +1826,13 @@
         <v>-1</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S16">
         <v>-1</v>
@@ -1844,13 +1844,13 @@
         <v>5</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W16">
         <v>6</v>
       </c>
       <c r="X16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y16">
         <v>8</v>
@@ -1903,13 +1903,13 @@
         <v>-1</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S17">
         <v>-1</v>
@@ -1924,7 +1924,7 @@
         <v>6</v>
       </c>
       <c r="W17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X17">
         <v>7</v>
@@ -1980,13 +1980,13 @@
         <v>-1</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S18">
         <v>-1</v>
@@ -2001,7 +2001,7 @@
         <v>8</v>
       </c>
       <c r="W18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X18">
         <v>8</v>
@@ -2036,13 +2036,13 @@
         <v>-1</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J19">
         <v>5</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L19">
         <v>5</v>
@@ -2057,13 +2057,13 @@
         <v>-1</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S19">
         <v>-1</v>
@@ -2075,13 +2075,13 @@
         <v>5</v>
       </c>
       <c r="V19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y19">
         <v>5</v>
@@ -2134,13 +2134,13 @@
         <v>-1</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
         <v>-1</v>
@@ -2152,13 +2152,13 @@
         <v>7</v>
       </c>
       <c r="V20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y20">
         <v>5</v>
@@ -2211,10 +2211,10 @@
         <v>-1</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R21">
         <v>-1</v>
@@ -2288,13 +2288,13 @@
         <v>-1</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S22">
         <v>-1</v>
@@ -2365,13 +2365,13 @@
         <v>-1</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S23">
         <v>-1</v>
@@ -2386,7 +2386,7 @@
         <v>8</v>
       </c>
       <c r="W23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X23">
         <v>8</v>
@@ -2442,13 +2442,13 @@
         <v>-1</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S24">
         <v>-1</v>
@@ -2519,13 +2519,13 @@
         <v>-1</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S25">
         <v>-1</v>
@@ -2537,7 +2537,7 @@
         <v>5</v>
       </c>
       <c r="V25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W25">
         <v>6</v>
@@ -2596,13 +2596,13 @@
         <v>-1</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S26">
         <v>-1</v>
@@ -2617,10 +2617,10 @@
         <v>6</v>
       </c>
       <c r="W26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y26">
         <v>6</v>
@@ -2664,7 +2664,7 @@
         <v>9</v>
       </c>
       <c r="M27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2673,13 +2673,13 @@
         <v>-1</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S27">
         <v>-1</v>
@@ -2691,7 +2691,7 @@
         <v>8</v>
       </c>
       <c r="V27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W27">
         <v>7</v>
@@ -2700,7 +2700,7 @@
         <v>9</v>
       </c>
       <c r="Y27">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -2777,7 +2777,7 @@
         <v>58.33</v>
       </c>
       <c r="H2">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -2788,7 +2788,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>46</v>
@@ -2800,27 +2800,27 @@
         <v>18</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F3">
         <v>75</v>
       </c>
       <c r="G3">
-        <v>20.83</v>
+        <v>25</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>4.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>47</v>
@@ -2829,19 +2829,19 @@
         <v>24</v>
       </c>
       <c r="D4">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="G4">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="H4">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -2861,16 +2861,16 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>83.33</v>
+        <v>95.83</v>
       </c>
       <c r="G5">
-        <v>16.67</v>
+        <v>4.17</v>
       </c>
       <c r="H5">
         <v>7.5</v>
@@ -2884,7 +2884,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>49</v>
@@ -2893,19 +2893,19 @@
         <v>24</v>
       </c>
       <c r="D6">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>87.5</v>
+        <v>95.83</v>
       </c>
       <c r="G6">
-        <v>12.5</v>
+        <v>4.17</v>
       </c>
       <c r="H6">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -2916,7 +2916,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
         <v>50</v>
@@ -2925,19 +2925,19 @@
         <v>24</v>
       </c>
       <c r="D7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>91.67</v>
+        <v>95.83</v>
       </c>
       <c r="G7">
-        <v>8.33</v>
+        <v>4.17</v>
       </c>
       <c r="H7">
-        <v>7.7</v>
+        <v>7.1</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -2953,7 +2953,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2978,26 +2978,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>19330051920235</v>
-      </c>
-      <c r="B2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -3033,30 +3013,30 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>19330051920235</v>
+        <v>19330051920223</v>
       </c>
       <c r="B2" t="s">
         <v>55</v>
       </c>
       <c r="C2" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>95</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920223</v>
+        <v>19330051920430</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D3" t="s">
         <v>96</v>
@@ -3067,13 +3047,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920430</v>
+        <v>19330051920225</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D4" t="s">
         <v>97</v>
@@ -3084,13 +3064,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920225</v>
+        <v>19330051920226</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D5" t="s">
         <v>98</v>
@@ -3101,13 +3081,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920226</v>
+        <v>19330051920227</v>
       </c>
       <c r="B6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D6" t="s">
         <v>99</v>
@@ -3118,13 +3098,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920227</v>
+        <v>19330051920229</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
         <v>100</v>
@@ -3135,13 +3115,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920229</v>
+        <v>19330051920230</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C8" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="D8" t="s">
         <v>101</v>
@@ -3152,13 +3132,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920230</v>
+        <v>19330051920231</v>
       </c>
       <c r="B9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" t="s">
         <v>64</v>
-      </c>
-      <c r="C9" t="s">
-        <v>85</v>
       </c>
       <c r="D9" t="s">
         <v>102</v>
@@ -3169,13 +3149,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920231</v>
+        <v>19330051920232</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C10" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="D10" t="s">
         <v>103</v>
@@ -3186,10 +3166,10 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920232</v>
+        <v>19330051920233</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C11" t="s">
         <v>86</v>
@@ -3203,10 +3183,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920233</v>
+        <v>19330051920234</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C12" t="s">
         <v>87</v>
@@ -3220,10 +3200,10 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920234</v>
+        <v>19330051920429</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C13" t="s">
         <v>88</v>
@@ -3237,13 +3217,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920429</v>
+        <v>19330051920235</v>
       </c>
       <c r="B14" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D14" t="s">
         <v>107</v>
@@ -3257,10 +3237,10 @@
         <v>19330051920236</v>
       </c>
       <c r="B15" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C15" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D15" t="s">
         <v>108</v>
@@ -3274,10 +3254,10 @@
         <v>19330051920237</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C16" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D16" t="s">
         <v>109</v>
@@ -3291,10 +3271,10 @@
         <v>19330051920228</v>
       </c>
       <c r="B17" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D17" t="s">
         <v>110</v>
@@ -3308,10 +3288,10 @@
         <v>19330051420227</v>
       </c>
       <c r="B18" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C18" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D18" t="s">
         <v>111</v>
@@ -3325,10 +3305,10 @@
         <v>19330051920404</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C19" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D19" t="s">
         <v>112</v>
@@ -3342,10 +3322,10 @@
         <v>19330051920240</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C20" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D20" t="s">
         <v>113</v>
@@ -3359,10 +3339,10 @@
         <v>19330051920239</v>
       </c>
       <c r="B21" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D21" t="s">
         <v>114</v>
@@ -3376,10 +3356,10 @@
         <v>19330051920242</v>
       </c>
       <c r="B22" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C22" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D22" t="s">
         <v>115</v>
@@ -3393,10 +3373,10 @@
         <v>19330051920243</v>
       </c>
       <c r="B23" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C23" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D23" t="s">
         <v>116</v>
@@ -3410,10 +3390,10 @@
         <v>19330051920244</v>
       </c>
       <c r="B24" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C24" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D24" t="s">
         <v>117</v>
@@ -3427,10 +3407,10 @@
         <v>19330051920245</v>
       </c>
       <c r="B25" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C25" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D25" t="s">
         <v>118</v>
@@ -3446,7 +3426,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3481,19 +3461,19 @@
         <v>19330051920227</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="D2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -3504,13 +3484,13 @@
         <v>19330051920227</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="D3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -3524,22 +3504,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920233</v>
+        <v>19330051920235</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -3547,22 +3527,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920233</v>
+        <v>19330051920235</v>
       </c>
       <c r="B5" t="s">
         <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -3570,19 +3550,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051420227</v>
+        <v>19330051920237</v>
       </c>
       <c r="B6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" t="s">
         <v>73</v>
       </c>
-      <c r="C6" t="s">
-        <v>91</v>
-      </c>
       <c r="D6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
         <v>46</v>
@@ -3593,16 +3573,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051420227</v>
+        <v>19330051920237</v>
       </c>
       <c r="B7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" t="s">
         <v>73</v>
       </c>
-      <c r="C7" t="s">
-        <v>91</v>
-      </c>
       <c r="D7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -3616,22 +3596,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920223</v>
+        <v>19330051920243</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="C8" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -3639,16 +3619,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920430</v>
+        <v>19330051920243</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="D9" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -3662,16 +3642,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920225</v>
+        <v>19330051920223</v>
       </c>
       <c r="B10" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C10" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
@@ -3685,16 +3665,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920230</v>
+        <v>19330051920430</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C11" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D11" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -3708,16 +3688,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920236</v>
+        <v>19330051920225</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="C12" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="D12" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
@@ -3731,16 +3711,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920239</v>
+        <v>19330051920230</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C13" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="D13" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -3754,16 +3734,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19330051920242</v>
+        <v>19330051920233</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="C14" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="D14" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
@@ -3777,24 +3757,93 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>19330051920244</v>
+        <v>19330051920236</v>
       </c>
       <c r="B15" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="C15" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D15" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>19330051420227</v>
+      </c>
+      <c r="B16" t="s">
+        <v>71</v>
+      </c>
+      <c r="C16" t="s">
+        <v>90</v>
+      </c>
+      <c r="D16" t="s">
+        <v>111</v>
+      </c>
+      <c r="E16" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" t="s">
+        <v>45</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>19330051920239</v>
+      </c>
+      <c r="B17" t="s">
+        <v>74</v>
+      </c>
+      <c r="C17" t="s">
+        <v>92</v>
+      </c>
+      <c r="D17" t="s">
+        <v>114</v>
+      </c>
+      <c r="E17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" t="s">
+        <v>45</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>19330051920242</v>
+      </c>
+      <c r="B18" t="s">
+        <v>75</v>
+      </c>
+      <c r="C18" t="s">
+        <v>66</v>
+      </c>
+      <c r="D18" t="s">
+        <v>115</v>
+      </c>
+      <c r="E18" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" t="s">
+        <v>45</v>
+      </c>
+      <c r="G18">
         <v>5</v>
       </c>
     </row>

--- a/grupos/6APM - Estadisticos 20212.xlsx
+++ b/grupos/6APM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="119">
   <si>
     <t>Materia</t>
   </si>
@@ -155,22 +155,22 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
+    <t>Ortega Valle Manuel</t>
+  </si>
+  <si>
     <t>Duran Amezcua María Angélica</t>
   </si>
   <si>
+    <t>Rodriguez Roman Marisol</t>
+  </si>
+  <si>
     <t>Herrera Serrano Mayra Iliana</t>
-  </si>
-  <si>
-    <t>Rodriguez Roman Marisol</t>
-  </si>
-  <si>
-    <t>Ochoa Martínez Mayeli</t>
-  </si>
-  <si>
-    <t>Velasco Sánchez David</t>
-  </si>
-  <si>
-    <t>Ortega Valle Manuel</t>
   </si>
   <si>
     <t>NC</t>
@@ -896,10 +896,10 @@
         <v>5</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P4">
         <v>6</v>
@@ -911,7 +911,7 @@
         <v>8</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T4">
         <v>7</v>
@@ -929,7 +929,7 @@
         <v>7</v>
       </c>
       <c r="Y4">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -973,10 +973,10 @@
         <v>5</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P5">
         <v>8</v>
@@ -988,10 +988,10 @@
         <v>7</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U5">
         <v>7</v>
@@ -1006,7 +1006,7 @@
         <v>7</v>
       </c>
       <c r="Y5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1050,10 +1050,10 @@
         <v>5</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P6">
         <v>8</v>
@@ -1065,7 +1065,7 @@
         <v>9</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T6">
         <v>7</v>
@@ -1083,7 +1083,7 @@
         <v>9</v>
       </c>
       <c r="Y6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1109,7 +1109,7 @@
         <v>5</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I7">
         <v>6</v>
@@ -1127,10 +1127,10 @@
         <v>5</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P7">
         <v>6</v>
@@ -1142,13 +1142,13 @@
         <v>5</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V7">
         <v>6</v>
@@ -1160,7 +1160,7 @@
         <v>7</v>
       </c>
       <c r="Y7">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1186,7 +1186,7 @@
         <v>6</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I8">
         <v>6</v>
@@ -1204,10 +1204,10 @@
         <v>5</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P8">
         <v>8</v>
@@ -1219,13 +1219,13 @@
         <v>8</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V8">
         <v>8</v>
@@ -1237,7 +1237,7 @@
         <v>7</v>
       </c>
       <c r="Y8">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1281,10 +1281,10 @@
         <v>7</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P9">
         <v>9</v>
@@ -1296,7 +1296,7 @@
         <v>8</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T9">
         <v>7</v>
@@ -1358,10 +1358,10 @@
         <v>7</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P10">
         <v>8</v>
@@ -1373,7 +1373,7 @@
         <v>8</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T10">
         <v>8</v>
@@ -1435,10 +1435,10 @@
         <v>5</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P11">
         <v>8</v>
@@ -1450,10 +1450,10 @@
         <v>8</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U11">
         <v>7</v>
@@ -1468,7 +1468,7 @@
         <v>8</v>
       </c>
       <c r="Y11">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1512,10 +1512,10 @@
         <v>5</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P12">
         <v>5</v>
@@ -1527,13 +1527,13 @@
         <v>5</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V12">
         <v>5</v>
@@ -1545,7 +1545,7 @@
         <v>5</v>
       </c>
       <c r="Y12">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1589,10 +1589,10 @@
         <v>8</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P13">
         <v>9</v>
@@ -1604,10 +1604,10 @@
         <v>9</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U13">
         <v>8</v>
@@ -1666,10 +1666,10 @@
         <v>5</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P14">
         <v>7</v>
@@ -1681,7 +1681,7 @@
         <v>9</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T14">
         <v>6</v>
@@ -1699,7 +1699,7 @@
         <v>7</v>
       </c>
       <c r="Y14">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1740,13 +1740,13 @@
         <v>10</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P15">
         <v>7</v>
@@ -1758,10 +1758,10 @@
         <v>10</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U15">
         <v>8</v>
@@ -1820,10 +1820,10 @@
         <v>8</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P16">
         <v>7</v>
@@ -1835,13 +1835,13 @@
         <v>8</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V16">
         <v>6</v>
@@ -1853,7 +1853,7 @@
         <v>6</v>
       </c>
       <c r="Y16">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1894,13 +1894,13 @@
         <v>7</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P17">
         <v>7</v>
@@ -1912,7 +1912,7 @@
         <v>8</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T17">
         <v>8</v>
@@ -1930,7 +1930,7 @@
         <v>7</v>
       </c>
       <c r="Y17">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1974,10 +1974,10 @@
         <v>5</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P18">
         <v>8</v>
@@ -1989,7 +1989,7 @@
         <v>9</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T18">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>8</v>
       </c>
       <c r="Y18">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2033,7 +2033,7 @@
         <v>6</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I19">
         <v>5</v>
@@ -2051,10 +2051,10 @@
         <v>5</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P19">
         <v>7</v>
@@ -2066,13 +2066,13 @@
         <v>8</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T19">
         <v>6</v>
       </c>
       <c r="U19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V19">
         <v>6</v>
@@ -2084,7 +2084,7 @@
         <v>6</v>
       </c>
       <c r="Y19">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2125,13 +2125,13 @@
         <v>5</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P20">
         <v>7</v>
@@ -2143,10 +2143,10 @@
         <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U20">
         <v>7</v>
@@ -2161,7 +2161,7 @@
         <v>8</v>
       </c>
       <c r="Y20">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2205,10 +2205,10 @@
         <v>8</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P21">
         <v>8</v>
@@ -2217,13 +2217,13 @@
         <v>8</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U21">
         <v>8</v>
@@ -2282,10 +2282,10 @@
         <v>5</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P22">
         <v>8</v>
@@ -2297,13 +2297,13 @@
         <v>8</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V22">
         <v>8</v>
@@ -2315,7 +2315,7 @@
         <v>9</v>
       </c>
       <c r="Y22">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2359,10 +2359,10 @@
         <v>10</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P23">
         <v>9</v>
@@ -2374,10 +2374,10 @@
         <v>8</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U23">
         <v>7</v>
@@ -2392,7 +2392,7 @@
         <v>8</v>
       </c>
       <c r="Y23">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2436,10 +2436,10 @@
         <v>5</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P24">
         <v>8</v>
@@ -2451,7 +2451,7 @@
         <v>8</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T24">
         <v>7</v>
@@ -2469,7 +2469,7 @@
         <v>8</v>
       </c>
       <c r="Y24">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2513,10 +2513,10 @@
         <v>5</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P25">
         <v>7</v>
@@ -2528,13 +2528,13 @@
         <v>7</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T25">
         <v>6</v>
       </c>
       <c r="U25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V25">
         <v>6</v>
@@ -2546,7 +2546,7 @@
         <v>6</v>
       </c>
       <c r="Y25">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2587,13 +2587,13 @@
         <v>5</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P26">
         <v>7</v>
@@ -2605,13 +2605,13 @@
         <v>8</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V26">
         <v>6</v>
@@ -2667,10 +2667,10 @@
         <v>10</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P27">
         <v>8</v>
@@ -2682,7 +2682,7 @@
         <v>9</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T27">
         <v>9</v>
@@ -2756,7 +2756,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>45</v>
@@ -2765,19 +2765,19 @@
         <v>24</v>
       </c>
       <c r="D2">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>41.67</v>
+        <v>95.83</v>
       </c>
       <c r="G2">
-        <v>58.33</v>
+        <v>4.17</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -2788,7 +2788,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>46</v>
@@ -2797,19 +2797,19 @@
         <v>24</v>
       </c>
       <c r="D3">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>75</v>
+        <v>95.83</v>
       </c>
       <c r="G3">
-        <v>25</v>
+        <v>4.17</v>
       </c>
       <c r="H3">
-        <v>6.6</v>
+        <v>7.7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -2820,7 +2820,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>47</v>
@@ -2829,19 +2829,19 @@
         <v>24</v>
       </c>
       <c r="D4">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>87.5</v>
+        <v>95.83</v>
       </c>
       <c r="G4">
-        <v>12.5</v>
+        <v>4.17</v>
       </c>
       <c r="H4">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -2852,7 +2852,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>48</v>
@@ -2861,19 +2861,19 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>95.83</v>
+        <v>100</v>
       </c>
       <c r="G5">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>7.5</v>
+        <v>6.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -2884,7 +2884,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>49</v>
@@ -2893,19 +2893,19 @@
         <v>24</v>
       </c>
       <c r="D6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>95.83</v>
+        <v>100</v>
       </c>
       <c r="G6">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>7.7</v>
+        <v>7.2</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -2916,7 +2916,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>50</v>
@@ -2925,19 +2925,19 @@
         <v>24</v>
       </c>
       <c r="D7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>95.83</v>
+        <v>100</v>
       </c>
       <c r="G7">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3426,7 +3426,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3456,397 +3456,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>19330051920227</v>
-      </c>
-      <c r="B2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D2" t="s">
-        <v>99</v>
-      </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>19330051920227</v>
-      </c>
-      <c r="B3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C3" t="s">
-        <v>83</v>
-      </c>
-      <c r="D3" t="s">
-        <v>99</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>19330051920235</v>
-      </c>
-      <c r="B4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C4" t="s">
-        <v>83</v>
-      </c>
-      <c r="D4" t="s">
-        <v>107</v>
-      </c>
-      <c r="E4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>19330051920235</v>
-      </c>
-      <c r="B5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C5" t="s">
-        <v>83</v>
-      </c>
-      <c r="D5" t="s">
-        <v>107</v>
-      </c>
-      <c r="E5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" t="s">
-        <v>46</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>19330051920237</v>
-      </c>
-      <c r="B6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D6" t="s">
-        <v>109</v>
-      </c>
-      <c r="E6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" t="s">
-        <v>46</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>19330051920237</v>
-      </c>
-      <c r="B7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C7" t="s">
-        <v>73</v>
-      </c>
-      <c r="D7" t="s">
-        <v>109</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>45</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>19330051920243</v>
-      </c>
-      <c r="B8" t="s">
-        <v>76</v>
-      </c>
-      <c r="C8" t="s">
-        <v>93</v>
-      </c>
-      <c r="D8" t="s">
-        <v>116</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>46</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>19330051920243</v>
-      </c>
-      <c r="B9" t="s">
-        <v>76</v>
-      </c>
-      <c r="C9" t="s">
-        <v>93</v>
-      </c>
-      <c r="D9" t="s">
-        <v>116</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>45</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>19330051920223</v>
-      </c>
-      <c r="B10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C10" t="s">
-        <v>79</v>
-      </c>
-      <c r="D10" t="s">
-        <v>95</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>45</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>19330051920430</v>
-      </c>
-      <c r="B11" t="s">
-        <v>56</v>
-      </c>
-      <c r="C11" t="s">
-        <v>80</v>
-      </c>
-      <c r="D11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>45</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>19330051920225</v>
-      </c>
-      <c r="B12" t="s">
-        <v>57</v>
-      </c>
-      <c r="C12" t="s">
-        <v>81</v>
-      </c>
-      <c r="D12" t="s">
-        <v>97</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>45</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>19330051920230</v>
-      </c>
-      <c r="B13" t="s">
-        <v>61</v>
-      </c>
-      <c r="C13" t="s">
-        <v>84</v>
-      </c>
-      <c r="D13" t="s">
-        <v>101</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>45</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>19330051920233</v>
-      </c>
-      <c r="B14" t="s">
-        <v>64</v>
-      </c>
-      <c r="C14" t="s">
-        <v>86</v>
-      </c>
-      <c r="D14" t="s">
-        <v>104</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>45</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>19330051920236</v>
-      </c>
-      <c r="B15" t="s">
-        <v>68</v>
-      </c>
-      <c r="C15" t="s">
-        <v>66</v>
-      </c>
-      <c r="D15" t="s">
-        <v>108</v>
-      </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
-        <v>45</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>19330051420227</v>
-      </c>
-      <c r="B16" t="s">
-        <v>71</v>
-      </c>
-      <c r="C16" t="s">
-        <v>90</v>
-      </c>
-      <c r="D16" t="s">
-        <v>111</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>45</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>19330051920239</v>
-      </c>
-      <c r="B17" t="s">
-        <v>74</v>
-      </c>
-      <c r="C17" t="s">
-        <v>92</v>
-      </c>
-      <c r="D17" t="s">
-        <v>114</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>45</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>19330051920242</v>
-      </c>
-      <c r="B18" t="s">
-        <v>75</v>
-      </c>
-      <c r="C18" t="s">
-        <v>66</v>
-      </c>
-      <c r="D18" t="s">
-        <v>115</v>
-      </c>
-      <c r="E18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G18">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
